--- a/testdata/configuration_environment.xlsx
+++ b/testdata/configuration_environment.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="65">
   <si>
     <t>This document was exported from Numbers. Each table was converted to an Excel worksheet. All other objects on each Numbers sheet were placed on separate worksheets. Please be aware that formula calculations may differ in Excel.</t>
   </si>

--- a/testdata/configuration_environment.xlsx
+++ b/testdata/configuration_environment.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView activeTab="1" windowHeight="12300" windowWidth="28800"/>
+    <workbookView windowWidth="23040" windowHeight="9000" activeTab="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Export Summary" r:id="rId1" sheetId="1"/>
-    <sheet name="Sheet1" r:id="rId2" sheetId="2"/>
-    <sheet name="Conn" r:id="rId3" sheetId="3"/>
+    <sheet name="Export Summary" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
+    <sheet name="Conn" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="65">
   <si>
     <t>This document was exported from Numbers. Each table was converted to an Excel worksheet. All other objects on each Numbers sheet were placed on separate worksheets. Please be aware that formula calculations may differ in Excel.</t>
   </si>
@@ -196,25 +196,25 @@
     <t>jdbc:sqlserver://10.1.133.30;Database=iBankingRaiffeisenV4;User Id=sa;Password=Cerkasov123;integratedSecurity=false;</t>
   </si>
   <si>
+    <t>ON</t>
+  </si>
+  <si>
+    <t>\\10.11.1.158\03. TEST Team\NLB SLO\FileShare\UAT</t>
+  </si>
+  <si>
+    <t>MYSQL</t>
+  </si>
+  <si>
+    <t>jdbc:mysql://172.20.1.100:3306/dbnlbreport?user=adm1n&amp;password=Beograd123!&amp;useSSL=false</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>UAT 06 07 2023 09:36:41</t>
+  </si>
+  <si>
     <t>si.nlb.klik.uat</t>
-  </si>
-  <si>
-    <t>ON</t>
-  </si>
-  <si>
-    <t>\\10.11.1.158\03. TEST Team\NLB SLO\FileShare\UAT</t>
-  </si>
-  <si>
-    <t>MYSQL</t>
-  </si>
-  <si>
-    <t>jdbc:mysql://172.20.1.100:3306/dbnlbreport?user=adm1n&amp;password=Beograd123!&amp;useSSL=false</t>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>UAT 06 07 2023 09:36:41</t>
   </si>
   <si>
     <t>co.infinum.nlb.uat:id/</t>
@@ -944,263 +944,263 @@
     </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0" borderId="0" fillId="0" fontId="0" numFmtId="0"/>
-    <xf applyAlignment="0" applyBorder="0" applyFill="0" applyFont="0" applyProtection="0" borderId="0" fillId="0" fontId="2" numFmtId="176">
-      <alignment vertical="center"/>
-    </xf>
-    <xf applyAlignment="0" applyBorder="0" applyFill="0" applyFont="0" applyProtection="0" borderId="0" fillId="0" fontId="2" numFmtId="44">
-      <alignment vertical="center"/>
-    </xf>
-    <xf applyAlignment="0" applyBorder="0" applyFill="0" applyFont="0" applyProtection="0" borderId="0" fillId="0" fontId="2" numFmtId="9">
-      <alignment vertical="center"/>
-    </xf>
-    <xf applyAlignment="0" applyBorder="0" applyFill="0" applyFont="0" applyProtection="0" borderId="0" fillId="0" fontId="2" numFmtId="177">
-      <alignment vertical="center"/>
-    </xf>
-    <xf applyAlignment="0" applyBorder="0" applyFill="0" applyFont="0" applyProtection="0" borderId="0" fillId="0" fontId="2" numFmtId="42">
-      <alignment vertical="center"/>
-    </xf>
-    <xf applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0" borderId="0" fillId="0" fontId="3" numFmtId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0" borderId="0" fillId="0" fontId="7" numFmtId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf applyAlignment="0" applyFont="0" applyNumberFormat="0" applyProtection="0" borderId="16" fillId="5" fontId="2" numFmtId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0" borderId="0" fillId="0" fontId="8" numFmtId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0" borderId="0" fillId="0" fontId="9" numFmtId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0" borderId="0" fillId="0" fontId="10" numFmtId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0" borderId="17" fillId="0" fontId="11" numFmtId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0" borderId="17" fillId="0" fontId="12" numFmtId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0" borderId="18" fillId="0" fontId="13" numFmtId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0" borderId="0" fillId="0" fontId="13" numFmtId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf applyAlignment="0" applyNumberFormat="0" applyProtection="0" borderId="19" fillId="6" fontId="14" numFmtId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf applyAlignment="0" applyNumberFormat="0" applyProtection="0" borderId="20" fillId="7" fontId="15" numFmtId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf applyAlignment="0" applyNumberFormat="0" applyProtection="0" borderId="19" fillId="7" fontId="16" numFmtId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf applyAlignment="0" applyNumberFormat="0" applyProtection="0" borderId="21" fillId="8" fontId="17" numFmtId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0" borderId="22" fillId="0" fontId="18" numFmtId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0" borderId="23" fillId="0" fontId="19" numFmtId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0" borderId="0" fillId="9" fontId="20" numFmtId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0" borderId="0" fillId="10" fontId="21" numFmtId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0" borderId="0" fillId="11" fontId="22" numFmtId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0" borderId="0" fillId="12" fontId="23" numFmtId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0" borderId="0" fillId="13" fontId="24" numFmtId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0" borderId="0" fillId="14" fontId="24" numFmtId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0" borderId="0" fillId="15" fontId="23" numFmtId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0" borderId="0" fillId="16" fontId="23" numFmtId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0" borderId="0" fillId="17" fontId="24" numFmtId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0" borderId="0" fillId="18" fontId="24" numFmtId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0" borderId="0" fillId="19" fontId="23" numFmtId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0" borderId="0" fillId="20" fontId="23" numFmtId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0" borderId="0" fillId="21" fontId="24" numFmtId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0" borderId="0" fillId="22" fontId="24" numFmtId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0" borderId="0" fillId="23" fontId="23" numFmtId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0" borderId="0" fillId="24" fontId="23" numFmtId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0" borderId="0" fillId="25" fontId="24" numFmtId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0" borderId="0" fillId="26" fontId="24" numFmtId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0" borderId="0" fillId="27" fontId="23" numFmtId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0" borderId="0" fillId="28" fontId="23" numFmtId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0" borderId="0" fillId="29" fontId="24" numFmtId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0" borderId="0" fillId="30" fontId="24" numFmtId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0" borderId="0" fillId="31" fontId="23" numFmtId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0" borderId="0" fillId="32" fontId="23" numFmtId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0" borderId="0" fillId="33" fontId="24" numFmtId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0" borderId="0" fillId="34" fontId="24" numFmtId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0" borderId="0" fillId="35" fontId="23" numFmtId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="16" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="19" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="20" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="19" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="22" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="23" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="33">
-    <xf applyAlignment="1" applyFont="1" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0"/>
-    <xf applyAlignment="1" applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0"/>
-    <xf applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1" borderId="1" fillId="2" fontId="1" numFmtId="49" xfId="0"/>
-    <xf applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1" borderId="1" fillId="2" fontId="0" numFmtId="49" xfId="0"/>
-    <xf applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" borderId="1" fillId="2" fontId="0" numFmtId="0" xfId="0"/>
-    <xf applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1" borderId="1" fillId="2" fontId="0" numFmtId="0" xfId="0"/>
-    <xf applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1" borderId="2" fillId="2" fontId="0" numFmtId="49" xfId="0"/>
-    <xf applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1" borderId="3" fillId="2" fontId="0" numFmtId="49" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1" borderId="4" fillId="2" fontId="0" numFmtId="49" xfId="0"/>
-    <xf applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1" borderId="5" fillId="2" fontId="0" numFmtId="49" xfId="0"/>
-    <xf applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1" borderId="6" fillId="2" fontId="0" numFmtId="49" xfId="0"/>
-    <xf applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" borderId="6" fillId="2" fontId="0" numFmtId="0" xfId="0"/>
-    <xf applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" borderId="7" fillId="2" fontId="0" numFmtId="0" xfId="0"/>
-    <xf applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1" applyProtection="1" borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" borderId="8" fillId="2" fontId="0" numFmtId="0" xfId="0"/>
-    <xf applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" borderId="9" fillId="2" fontId="0" numFmtId="0" xfId="0"/>
-    <xf applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" borderId="10" fillId="2" fontId="0" numFmtId="0" xfId="0"/>
-    <xf applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" borderId="11" fillId="2" fontId="0" numFmtId="0" xfId="0"/>
-    <xf applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" borderId="0" fillId="2" fontId="0" numFmtId="0" xfId="0"/>
-    <xf applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" borderId="12" fillId="2" fontId="0" numFmtId="0" xfId="0"/>
-    <xf applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1" borderId="0" fillId="2" fontId="4" numFmtId="49" xfId="0">
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1" borderId="0" fillId="2" fontId="5" numFmtId="49" xfId="0">
+    <xf numFmtId="49" fontId="5" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1" borderId="0" fillId="3" fontId="4" numFmtId="49" xfId="0">
+    <xf numFmtId="49" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" borderId="0" fillId="3" fontId="4" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" borderId="0" fillId="4" fontId="4" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1" borderId="0" fillId="4" fontId="4" numFmtId="49" xfId="0">
+    <xf numFmtId="49" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1" borderId="0" fillId="4" fontId="6" numFmtId="49" xfId="0">
+    <xf numFmtId="49" fontId="6" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" borderId="13" fillId="2" fontId="0" numFmtId="0" xfId="0"/>
-    <xf applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" borderId="14" fillId="4" fontId="4" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1" borderId="14" fillId="4" fontId="4" numFmtId="49" xfId="0">
+    <xf numFmtId="49" fontId="4" fillId="4" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1" borderId="14" fillId="4" fontId="6" numFmtId="49" xfId="0">
+    <xf numFmtId="49" fontId="6" fillId="4" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" borderId="15" fillId="2" fontId="0" numFmtId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
-    <cellStyle builtinId="0" name="Normal" xfId="0"/>
-    <cellStyle builtinId="3" name="Comma" xfId="1"/>
-    <cellStyle builtinId="4" name="Currency" xfId="2"/>
-    <cellStyle builtinId="5" name="Percent" xfId="3"/>
-    <cellStyle builtinId="6" name="Comma [0]" xfId="4"/>
-    <cellStyle builtinId="7" name="Currency [0]" xfId="5"/>
-    <cellStyle builtinId="8" name="Hyperlink" xfId="6"/>
-    <cellStyle builtinId="9" name="Followed Hyperlink" xfId="7"/>
-    <cellStyle builtinId="10" name="Note" xfId="8"/>
-    <cellStyle builtinId="11" name="Warning Text" xfId="9"/>
-    <cellStyle builtinId="15" name="Title" xfId="10"/>
-    <cellStyle builtinId="53" name="CExplanatory Text" xfId="11"/>
-    <cellStyle builtinId="16" name="Heading 1" xfId="12"/>
-    <cellStyle builtinId="17" name="Heading 2" xfId="13"/>
-    <cellStyle builtinId="18" name="Heading 3" xfId="14"/>
-    <cellStyle builtinId="19" name="Heading 4" xfId="15"/>
-    <cellStyle builtinId="20" name="Input" xfId="16"/>
-    <cellStyle builtinId="21" name="Output" xfId="17"/>
-    <cellStyle builtinId="22" name="Calculation" xfId="18"/>
-    <cellStyle builtinId="23" name="Check Cell" xfId="19"/>
-    <cellStyle builtinId="24" name="Linked Cell" xfId="20"/>
-    <cellStyle builtinId="25" name="Total" xfId="21"/>
-    <cellStyle builtinId="26" name="Good" xfId="22"/>
-    <cellStyle builtinId="27" name="Bad" xfId="23"/>
-    <cellStyle builtinId="28" name="Neutral" xfId="24"/>
-    <cellStyle builtinId="29" name="Accent1" xfId="25"/>
-    <cellStyle builtinId="30" name="20% - Accent1" xfId="26"/>
-    <cellStyle builtinId="31" name="40% - Accent1" xfId="27"/>
-    <cellStyle builtinId="32" name="60% - Accent1" xfId="28"/>
-    <cellStyle builtinId="33" name="Accent2" xfId="29"/>
-    <cellStyle builtinId="34" name="20% - Accent2" xfId="30"/>
-    <cellStyle builtinId="35" name="40% - Accent2" xfId="31"/>
-    <cellStyle builtinId="36" name="60% - Accent2" xfId="32"/>
-    <cellStyle builtinId="37" name="Accent3" xfId="33"/>
-    <cellStyle builtinId="38" name="20% - Accent3" xfId="34"/>
-    <cellStyle builtinId="39" name="40% - Accent3" xfId="35"/>
-    <cellStyle builtinId="40" name="60% - Accent3" xfId="36"/>
-    <cellStyle builtinId="41" name="Accent4" xfId="37"/>
-    <cellStyle builtinId="42" name="20% - Accent4" xfId="38"/>
-    <cellStyle builtinId="43" name="40% - Accent4" xfId="39"/>
-    <cellStyle builtinId="44" name="60% - Accent4" xfId="40"/>
-    <cellStyle builtinId="45" name="Accent5" xfId="41"/>
-    <cellStyle builtinId="46" name="20% - Accent5" xfId="42"/>
-    <cellStyle builtinId="47" name="40% - Accent5" xfId="43"/>
-    <cellStyle builtinId="48" name="60% - Accent5" xfId="44"/>
-    <cellStyle builtinId="49" name="Accent6" xfId="45"/>
-    <cellStyle builtinId="50" name="20% - Accent6" xfId="46"/>
-    <cellStyle builtinId="51" name="40% - Accent6" xfId="47"/>
-    <cellStyle builtinId="52" name="60% - Accent6" xfId="48"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Currency" xfId="2" builtinId="4"/>
+    <cellStyle name="Percent" xfId="3" builtinId="5"/>
+    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
+    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
+    <cellStyle name="Link" xfId="6" builtinId="8"/>
+    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
+    <cellStyle name="Note" xfId="8" builtinId="10"/>
+    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
+    <cellStyle name="Title" xfId="10" builtinId="15"/>
+    <cellStyle name="Explanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
+    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
+    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
+    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
+    <cellStyle name="Input" xfId="16" builtinId="20"/>
+    <cellStyle name="Output" xfId="17" builtinId="21"/>
+    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
+    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
+    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
+    <cellStyle name="Total" xfId="21" builtinId="25"/>
+    <cellStyle name="Good" xfId="22" builtinId="26"/>
+    <cellStyle name="Bad" xfId="23" builtinId="27"/>
+    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
+    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
+    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
+    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
+    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
+    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
+    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0"/>
   <colors>
@@ -1381,7 +1381,7 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln algn="ctr" cap="flat" cmpd="sng" w="9525">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr">
               <a:shade val="95000"/>
@@ -1390,13 +1390,13 @@
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln algn="ctr" cap="flat" cmpd="sng" w="25400">
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln algn="ctr" cap="flat" cmpd="sng" w="38100">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -1441,7 +1441,7 @@
             </a:gs>
           </a:gsLst>
           <a:path path="circle">
-            <a:fillToRect b="180000" l="50000" r="50000" t="-80000"/>
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
           </a:path>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
@@ -1460,7 +1460,7 @@
             </a:gs>
           </a:gsLst>
           <a:path path="circle">
-            <a:fillToRect b="50000" l="50000" r="50000" t="50000"/>
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
           </a:path>
         </a:gradFill>
       </a:bgFillStyleLst>
@@ -1472,7 +1472,7 @@
         <a:solidFill>
           <a:srgbClr val="FFFFFF"/>
         </a:solidFill>
-        <a:ln cap="flat" w="25400">
+        <a:ln w="25400" cap="flat">
           <a:solidFill>
             <a:schemeClr val="accent1"/>
           </a:solidFill>
@@ -1480,11 +1480,11 @@
           <a:round/>
         </a:ln>
       </a:spPr>
-      <a:bodyPr anchor="ctr" bIns="45718" horzOverflow="overflow" lIns="45718" numCol="1" rIns="45718" rot="0" rtlCol="0" spcCol="38100" spcFirstLastPara="1" tIns="45718" upright="0" vert="horz" vertOverflow="overflow" wrap="square">
+      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="45718" tIns="45718" rIns="45718" bIns="45718" numCol="1" spcCol="38100" rtlCol="0" anchor="ctr" upright="0">
         <a:spAutoFit/>
       </a:bodyPr>
       <a:lstStyle>
-        <a:defPPr algn="l" defTabSz="914400" fontAlgn="auto" hangingPunct="0" indent="0" latinLnBrk="0" marL="0" marR="0" rtl="0">
+        <a:defPPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="0" hangingPunct="0">
           <a:lnSpc>
             <a:spcPct val="100000"/>
           </a:lnSpc>
@@ -1498,7 +1498,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" kumimoji="0" normalizeH="0" spc="0" strike="noStrike" sz="1100" u="none">
+          <a:defRPr kumimoji="0" sz="1100" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1513,7 +1513,7 @@
             <a:sym typeface="Helvetica Neue"/>
           </a:defRPr>
         </a:defPPr>
-        <a:lvl1pPr algn="l" defTabSz="914400" fontAlgn="auto" hangingPunct="0" indent="0" latinLnBrk="1" marL="0" marR="0" rtl="0">
+        <a:lvl1pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="1" hangingPunct="0">
           <a:lnSpc>
             <a:spcPct val="100000"/>
           </a:lnSpc>
@@ -1527,7 +1527,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" kumimoji="0" normalizeH="0" spc="0" strike="noStrike" sz="1800" u="none">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1538,7 +1538,7 @@
             <a:uFillTx/>
           </a:defRPr>
         </a:lvl1pPr>
-        <a:lvl2pPr algn="l" defTabSz="914400" fontAlgn="auto" hangingPunct="0" indent="0" latinLnBrk="1" marL="0" marR="0" rtl="0">
+        <a:lvl2pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="1" hangingPunct="0">
           <a:lnSpc>
             <a:spcPct val="100000"/>
           </a:lnSpc>
@@ -1552,7 +1552,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" kumimoji="0" normalizeH="0" spc="0" strike="noStrike" sz="1800" u="none">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1563,7 +1563,7 @@
             <a:uFillTx/>
           </a:defRPr>
         </a:lvl2pPr>
-        <a:lvl3pPr algn="l" defTabSz="914400" fontAlgn="auto" hangingPunct="0" indent="0" latinLnBrk="1" marL="0" marR="0" rtl="0">
+        <a:lvl3pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="1" hangingPunct="0">
           <a:lnSpc>
             <a:spcPct val="100000"/>
           </a:lnSpc>
@@ -1577,7 +1577,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" kumimoji="0" normalizeH="0" spc="0" strike="noStrike" sz="1800" u="none">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1588,7 +1588,7 @@
             <a:uFillTx/>
           </a:defRPr>
         </a:lvl3pPr>
-        <a:lvl4pPr algn="l" defTabSz="914400" fontAlgn="auto" hangingPunct="0" indent="0" latinLnBrk="1" marL="0" marR="0" rtl="0">
+        <a:lvl4pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="1" hangingPunct="0">
           <a:lnSpc>
             <a:spcPct val="100000"/>
           </a:lnSpc>
@@ -1602,7 +1602,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" kumimoji="0" normalizeH="0" spc="0" strike="noStrike" sz="1800" u="none">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1613,7 +1613,7 @@
             <a:uFillTx/>
           </a:defRPr>
         </a:lvl4pPr>
-        <a:lvl5pPr algn="l" defTabSz="914400" fontAlgn="auto" hangingPunct="0" indent="0" latinLnBrk="1" marL="0" marR="0" rtl="0">
+        <a:lvl5pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="1" hangingPunct="0">
           <a:lnSpc>
             <a:spcPct val="100000"/>
           </a:lnSpc>
@@ -1627,7 +1627,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" kumimoji="0" normalizeH="0" spc="0" strike="noStrike" sz="1800" u="none">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1638,7 +1638,7 @@
             <a:uFillTx/>
           </a:defRPr>
         </a:lvl5pPr>
-        <a:lvl6pPr algn="l" defTabSz="914400" fontAlgn="auto" hangingPunct="0" indent="0" latinLnBrk="1" marL="0" marR="0" rtl="0">
+        <a:lvl6pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="1" hangingPunct="0">
           <a:lnSpc>
             <a:spcPct val="100000"/>
           </a:lnSpc>
@@ -1652,7 +1652,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" kumimoji="0" normalizeH="0" spc="0" strike="noStrike" sz="1800" u="none">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1663,7 +1663,7 @@
             <a:uFillTx/>
           </a:defRPr>
         </a:lvl6pPr>
-        <a:lvl7pPr algn="l" defTabSz="914400" fontAlgn="auto" hangingPunct="0" indent="0" latinLnBrk="1" marL="0" marR="0" rtl="0">
+        <a:lvl7pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="1" hangingPunct="0">
           <a:lnSpc>
             <a:spcPct val="100000"/>
           </a:lnSpc>
@@ -1677,7 +1677,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" kumimoji="0" normalizeH="0" spc="0" strike="noStrike" sz="1800" u="none">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1688,7 +1688,7 @@
             <a:uFillTx/>
           </a:defRPr>
         </a:lvl7pPr>
-        <a:lvl8pPr algn="l" defTabSz="914400" fontAlgn="auto" hangingPunct="0" indent="0" latinLnBrk="1" marL="0" marR="0" rtl="0">
+        <a:lvl8pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="1" hangingPunct="0">
           <a:lnSpc>
             <a:spcPct val="100000"/>
           </a:lnSpc>
@@ -1702,7 +1702,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" kumimoji="0" normalizeH="0" spc="0" strike="noStrike" sz="1800" u="none">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1713,7 +1713,7 @@
             <a:uFillTx/>
           </a:defRPr>
         </a:lvl8pPr>
-        <a:lvl9pPr algn="l" defTabSz="914400" fontAlgn="auto" hangingPunct="0" indent="0" latinLnBrk="1" marL="0" marR="0" rtl="0">
+        <a:lvl9pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="1" hangingPunct="0">
           <a:lnSpc>
             <a:spcPct val="100000"/>
           </a:lnSpc>
@@ -1727,7 +1727,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" kumimoji="0" normalizeH="0" spc="0" strike="noStrike" sz="1800" u="none">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1755,7 +1755,7 @@
     <a:lnDef>
       <a:spPr>
         <a:noFill/>
-        <a:ln cap="flat" w="25400">
+        <a:ln w="25400" cap="flat">
           <a:solidFill>
             <a:schemeClr val="accent1"/>
           </a:solidFill>
@@ -1763,11 +1763,11 @@
           <a:round/>
         </a:ln>
       </a:spPr>
-      <a:bodyPr anchor="t" bIns="45719" horzOverflow="overflow" lIns="91439" numCol="1" rIns="91439" rot="0" rtlCol="0" spcCol="38100" spcFirstLastPara="1" tIns="45719" upright="0" vert="horz" vertOverflow="overflow" wrap="square">
+      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="91439" tIns="45719" rIns="91439" bIns="45719" numCol="1" spcCol="38100" rtlCol="0" anchor="t" upright="0">
         <a:noAutofit/>
       </a:bodyPr>
       <a:lstStyle>
-        <a:defPPr algn="l" defTabSz="914400" fontAlgn="auto" hangingPunct="0" indent="0" latinLnBrk="1" marL="0" marR="0" rtl="0">
+        <a:defPPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="1" hangingPunct="0">
           <a:lnSpc>
             <a:spcPct val="100000"/>
           </a:lnSpc>
@@ -1781,7 +1781,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" kumimoji="0" normalizeH="0" spc="0" strike="noStrike" sz="1800" u="none">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1792,7 +1792,7 @@
             <a:uFillTx/>
           </a:defRPr>
         </a:defPPr>
-        <a:lvl1pPr algn="l" defTabSz="914400" fontAlgn="auto" hangingPunct="0" indent="0" latinLnBrk="1" marL="0" marR="0" rtl="0">
+        <a:lvl1pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="1" hangingPunct="0">
           <a:lnSpc>
             <a:spcPct val="100000"/>
           </a:lnSpc>
@@ -1806,7 +1806,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" kumimoji="0" normalizeH="0" spc="0" strike="noStrike" sz="1800" u="none">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1817,7 +1817,7 @@
             <a:uFillTx/>
           </a:defRPr>
         </a:lvl1pPr>
-        <a:lvl2pPr algn="l" defTabSz="914400" fontAlgn="auto" hangingPunct="0" indent="0" latinLnBrk="1" marL="0" marR="0" rtl="0">
+        <a:lvl2pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="1" hangingPunct="0">
           <a:lnSpc>
             <a:spcPct val="100000"/>
           </a:lnSpc>
@@ -1831,7 +1831,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" kumimoji="0" normalizeH="0" spc="0" strike="noStrike" sz="1800" u="none">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1842,7 +1842,7 @@
             <a:uFillTx/>
           </a:defRPr>
         </a:lvl2pPr>
-        <a:lvl3pPr algn="l" defTabSz="914400" fontAlgn="auto" hangingPunct="0" indent="0" latinLnBrk="1" marL="0" marR="0" rtl="0">
+        <a:lvl3pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="1" hangingPunct="0">
           <a:lnSpc>
             <a:spcPct val="100000"/>
           </a:lnSpc>
@@ -1856,7 +1856,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" kumimoji="0" normalizeH="0" spc="0" strike="noStrike" sz="1800" u="none">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1867,7 +1867,7 @@
             <a:uFillTx/>
           </a:defRPr>
         </a:lvl3pPr>
-        <a:lvl4pPr algn="l" defTabSz="914400" fontAlgn="auto" hangingPunct="0" indent="0" latinLnBrk="1" marL="0" marR="0" rtl="0">
+        <a:lvl4pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="1" hangingPunct="0">
           <a:lnSpc>
             <a:spcPct val="100000"/>
           </a:lnSpc>
@@ -1881,7 +1881,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" kumimoji="0" normalizeH="0" spc="0" strike="noStrike" sz="1800" u="none">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1892,7 +1892,7 @@
             <a:uFillTx/>
           </a:defRPr>
         </a:lvl4pPr>
-        <a:lvl5pPr algn="l" defTabSz="914400" fontAlgn="auto" hangingPunct="0" indent="0" latinLnBrk="1" marL="0" marR="0" rtl="0">
+        <a:lvl5pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="1" hangingPunct="0">
           <a:lnSpc>
             <a:spcPct val="100000"/>
           </a:lnSpc>
@@ -1906,7 +1906,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" kumimoji="0" normalizeH="0" spc="0" strike="noStrike" sz="1800" u="none">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1917,7 +1917,7 @@
             <a:uFillTx/>
           </a:defRPr>
         </a:lvl5pPr>
-        <a:lvl6pPr algn="l" defTabSz="914400" fontAlgn="auto" hangingPunct="0" indent="0" latinLnBrk="1" marL="0" marR="0" rtl="0">
+        <a:lvl6pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="1" hangingPunct="0">
           <a:lnSpc>
             <a:spcPct val="100000"/>
           </a:lnSpc>
@@ -1931,7 +1931,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" kumimoji="0" normalizeH="0" spc="0" strike="noStrike" sz="1800" u="none">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1942,7 +1942,7 @@
             <a:uFillTx/>
           </a:defRPr>
         </a:lvl6pPr>
-        <a:lvl7pPr algn="l" defTabSz="914400" fontAlgn="auto" hangingPunct="0" indent="0" latinLnBrk="1" marL="0" marR="0" rtl="0">
+        <a:lvl7pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="1" hangingPunct="0">
           <a:lnSpc>
             <a:spcPct val="100000"/>
           </a:lnSpc>
@@ -1956,7 +1956,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" kumimoji="0" normalizeH="0" spc="0" strike="noStrike" sz="1800" u="none">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1967,7 +1967,7 @@
             <a:uFillTx/>
           </a:defRPr>
         </a:lvl7pPr>
-        <a:lvl8pPr algn="l" defTabSz="914400" fontAlgn="auto" hangingPunct="0" indent="0" latinLnBrk="1" marL="0" marR="0" rtl="0">
+        <a:lvl8pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="1" hangingPunct="0">
           <a:lnSpc>
             <a:spcPct val="100000"/>
           </a:lnSpc>
@@ -1981,7 +1981,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" kumimoji="0" normalizeH="0" spc="0" strike="noStrike" sz="1800" u="none">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1992,7 +1992,7 @@
             <a:uFillTx/>
           </a:defRPr>
         </a:lvl8pPr>
-        <a:lvl9pPr algn="l" defTabSz="914400" fontAlgn="auto" hangingPunct="0" indent="0" latinLnBrk="1" marL="0" marR="0" rtl="0">
+        <a:lvl9pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="1" hangingPunct="0">
           <a:lnSpc>
             <a:spcPct val="100000"/>
           </a:lnSpc>
@@ -2006,7 +2006,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" kumimoji="0" normalizeH="0" spc="0" strike="noStrike" sz="1800" u="none">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -2034,16 +2034,16 @@
     <a:txDef>
       <a:spPr>
         <a:noFill/>
-        <a:ln cap="flat" w="12700">
+        <a:ln w="12700" cap="flat">
           <a:noFill/>
           <a:miter lim="400000"/>
         </a:ln>
       </a:spPr>
-      <a:bodyPr anchor="t" bIns="45718" horzOverflow="overflow" lIns="45718" numCol="1" rIns="45718" rot="0" rtlCol="0" spcCol="38100" spcFirstLastPara="1" tIns="45718" upright="0" vert="horz" vertOverflow="overflow" wrap="square">
+      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="45718" tIns="45718" rIns="45718" bIns="45718" numCol="1" spcCol="38100" rtlCol="0" anchor="t" upright="0">
         <a:spAutoFit/>
       </a:bodyPr>
       <a:lstStyle>
-        <a:defPPr algn="l" defTabSz="914400" fontAlgn="auto" hangingPunct="0" indent="0" latinLnBrk="0" marL="0" marR="0" rtl="0">
+        <a:defPPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="0" hangingPunct="0">
           <a:lnSpc>
             <a:spcPct val="100000"/>
           </a:lnSpc>
@@ -2057,7 +2057,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" kumimoji="0" normalizeH="0" spc="0" strike="noStrike" sz="1100" u="none">
+          <a:defRPr kumimoji="0" sz="1100" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -2072,7 +2072,7 @@
             <a:sym typeface="Helvetica Neue"/>
           </a:defRPr>
         </a:defPPr>
-        <a:lvl1pPr algn="l" defTabSz="914400" fontAlgn="auto" hangingPunct="0" indent="0" latinLnBrk="1" marL="0" marR="0" rtl="0">
+        <a:lvl1pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="1" hangingPunct="0">
           <a:lnSpc>
             <a:spcPct val="100000"/>
           </a:lnSpc>
@@ -2086,7 +2086,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" kumimoji="0" normalizeH="0" spc="0" strike="noStrike" sz="1800" u="none">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -2097,7 +2097,7 @@
             <a:uFillTx/>
           </a:defRPr>
         </a:lvl1pPr>
-        <a:lvl2pPr algn="l" defTabSz="914400" fontAlgn="auto" hangingPunct="0" indent="0" latinLnBrk="1" marL="0" marR="0" rtl="0">
+        <a:lvl2pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="1" hangingPunct="0">
           <a:lnSpc>
             <a:spcPct val="100000"/>
           </a:lnSpc>
@@ -2111,7 +2111,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" kumimoji="0" normalizeH="0" spc="0" strike="noStrike" sz="1800" u="none">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -2122,7 +2122,7 @@
             <a:uFillTx/>
           </a:defRPr>
         </a:lvl2pPr>
-        <a:lvl3pPr algn="l" defTabSz="914400" fontAlgn="auto" hangingPunct="0" indent="0" latinLnBrk="1" marL="0" marR="0" rtl="0">
+        <a:lvl3pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="1" hangingPunct="0">
           <a:lnSpc>
             <a:spcPct val="100000"/>
           </a:lnSpc>
@@ -2136,7 +2136,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" kumimoji="0" normalizeH="0" spc="0" strike="noStrike" sz="1800" u="none">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -2147,7 +2147,7 @@
             <a:uFillTx/>
           </a:defRPr>
         </a:lvl3pPr>
-        <a:lvl4pPr algn="l" defTabSz="914400" fontAlgn="auto" hangingPunct="0" indent="0" latinLnBrk="1" marL="0" marR="0" rtl="0">
+        <a:lvl4pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="1" hangingPunct="0">
           <a:lnSpc>
             <a:spcPct val="100000"/>
           </a:lnSpc>
@@ -2161,7 +2161,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" kumimoji="0" normalizeH="0" spc="0" strike="noStrike" sz="1800" u="none">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -2172,7 +2172,7 @@
             <a:uFillTx/>
           </a:defRPr>
         </a:lvl4pPr>
-        <a:lvl5pPr algn="l" defTabSz="914400" fontAlgn="auto" hangingPunct="0" indent="0" latinLnBrk="1" marL="0" marR="0" rtl="0">
+        <a:lvl5pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="1" hangingPunct="0">
           <a:lnSpc>
             <a:spcPct val="100000"/>
           </a:lnSpc>
@@ -2186,7 +2186,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" kumimoji="0" normalizeH="0" spc="0" strike="noStrike" sz="1800" u="none">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -2197,7 +2197,7 @@
             <a:uFillTx/>
           </a:defRPr>
         </a:lvl5pPr>
-        <a:lvl6pPr algn="l" defTabSz="914400" fontAlgn="auto" hangingPunct="0" indent="0" latinLnBrk="1" marL="0" marR="0" rtl="0">
+        <a:lvl6pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="1" hangingPunct="0">
           <a:lnSpc>
             <a:spcPct val="100000"/>
           </a:lnSpc>
@@ -2211,7 +2211,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" kumimoji="0" normalizeH="0" spc="0" strike="noStrike" sz="1800" u="none">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -2222,7 +2222,7 @@
             <a:uFillTx/>
           </a:defRPr>
         </a:lvl6pPr>
-        <a:lvl7pPr algn="l" defTabSz="914400" fontAlgn="auto" hangingPunct="0" indent="0" latinLnBrk="1" marL="0" marR="0" rtl="0">
+        <a:lvl7pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="1" hangingPunct="0">
           <a:lnSpc>
             <a:spcPct val="100000"/>
           </a:lnSpc>
@@ -2236,7 +2236,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" kumimoji="0" normalizeH="0" spc="0" strike="noStrike" sz="1800" u="none">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -2247,7 +2247,7 @@
             <a:uFillTx/>
           </a:defRPr>
         </a:lvl7pPr>
-        <a:lvl8pPr algn="l" defTabSz="914400" fontAlgn="auto" hangingPunct="0" indent="0" latinLnBrk="1" marL="0" marR="0" rtl="0">
+        <a:lvl8pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="1" hangingPunct="0">
           <a:lnSpc>
             <a:spcPct val="100000"/>
           </a:lnSpc>
@@ -2261,7 +2261,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" kumimoji="0" normalizeH="0" spc="0" strike="noStrike" sz="1800" u="none">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -2272,7 +2272,7 @@
             <a:uFillTx/>
           </a:defRPr>
         </a:lvl8pPr>
-        <a:lvl9pPr algn="l" defTabSz="914400" fontAlgn="auto" hangingPunct="0" indent="0" latinLnBrk="1" marL="0" marR="0" rtl="0">
+        <a:lvl9pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="1" hangingPunct="0">
           <a:lnSpc>
             <a:spcPct val="100000"/>
           </a:lnSpc>
@@ -2286,7 +2286,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" kumimoji="0" normalizeH="0" spc="0" strike="noStrike" sz="1800" u="none">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -2316,33 +2316,33 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
-  <sheetFormatPr customHeight="1" defaultColWidth="10" defaultRowHeight="13" outlineLevelCol="4"/>
+  <dimension ref="A1:E12"/>
+  <sheetFormatPr defaultColWidth="10" defaultRowHeight="13" customHeight="1" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" customWidth="true" style="1" width="2.0" collapsed="true"/>
-    <col min="2" max="4" customWidth="true" style="1" width="30.5047619047619" collapsed="true"/>
-    <col min="5" max="256" customWidth="true" style="1" width="10.0" collapsed="true"/>
+    <col min="1" max="1" width="2" style="1" customWidth="1" collapsed="1"/>
+    <col min="2" max="4" width="30.5092592592593" style="1" customWidth="1" collapsed="1"/>
+    <col min="5" max="256" width="10" style="1" customWidth="1" collapsed="1"/>
   </cols>
   <sheetData>
-    <row customHeight="1" ht="15" r="1" spans="1:5">
+    <row r="1" ht="15" customHeight="1" spans="1:5">
       <c r="A1" s="15"/>
       <c r="B1" s="16"/>
       <c r="C1" s="16"/>
       <c r="D1" s="16"/>
       <c r="E1" s="17"/>
     </row>
-    <row customHeight="1" ht="15" r="2" spans="1:5">
+    <row r="2" ht="15" customHeight="1" spans="1:5">
       <c r="A2" s="18"/>
       <c r="B2" s="19"/>
       <c r="C2" s="19"/>
       <c r="D2" s="19"/>
       <c r="E2" s="20"/>
     </row>
-    <row customHeight="1" ht="8" r="3" spans="1:5">
+    <row r="3" ht="8" customHeight="1" spans="1:5">
       <c r="A3" s="18"/>
       <c r="B3" s="21" t="s">
         <v>0</v>
@@ -2351,28 +2351,28 @@
       <c r="D3" s="19"/>
       <c r="E3" s="20"/>
     </row>
-    <row customHeight="1" ht="15" r="4" spans="1:5">
+    <row r="4" ht="15" customHeight="1" spans="1:5">
       <c r="A4" s="18"/>
       <c r="B4" s="19"/>
       <c r="C4" s="19"/>
       <c r="D4" s="19"/>
       <c r="E4" s="20"/>
     </row>
-    <row customHeight="1" ht="15" r="5" spans="1:5">
+    <row r="5" ht="15" customHeight="1" spans="1:5">
       <c r="A5" s="18"/>
       <c r="B5" s="19"/>
       <c r="C5" s="19"/>
       <c r="D5" s="19"/>
       <c r="E5" s="20"/>
     </row>
-    <row customHeight="1" ht="15" r="6" spans="1:5">
+    <row r="6" ht="15" customHeight="1" spans="1:5">
       <c r="A6" s="18"/>
       <c r="B6" s="19"/>
       <c r="C6" s="19"/>
       <c r="D6" s="19"/>
       <c r="E6" s="20"/>
     </row>
-    <row customHeight="1" ht="19" r="7" spans="1:5">
+    <row r="7" ht="19" customHeight="1" spans="1:5">
       <c r="A7" s="18"/>
       <c r="B7" s="22" t="s">
         <v>1</v>
@@ -2385,14 +2385,14 @@
       </c>
       <c r="E7" s="20"/>
     </row>
-    <row customHeight="1" ht="15" r="8" spans="1:5">
+    <row r="8" ht="15" customHeight="1" spans="1:5">
       <c r="A8" s="18"/>
       <c r="B8" s="19"/>
       <c r="C8" s="19"/>
       <c r="D8" s="19"/>
       <c r="E8" s="20"/>
     </row>
-    <row customHeight="1" ht="17" r="9" spans="1:5">
+    <row r="9" ht="17" customHeight="1" spans="1:5">
       <c r="A9" s="18"/>
       <c r="B9" s="23" t="s">
         <v>4</v>
@@ -2401,7 +2401,7 @@
       <c r="D9" s="24"/>
       <c r="E9" s="20"/>
     </row>
-    <row customHeight="1" ht="17" r="10" spans="1:5">
+    <row r="10" ht="17" customHeight="1" spans="1:5">
       <c r="A10" s="18"/>
       <c r="B10" s="25"/>
       <c r="C10" s="26" t="s">
@@ -2412,7 +2412,7 @@
       </c>
       <c r="E10" s="20"/>
     </row>
-    <row customHeight="1" ht="17" r="11" spans="1:5">
+    <row r="11" ht="17" customHeight="1" spans="1:5">
       <c r="A11" s="18"/>
       <c r="B11" s="23" t="s">
         <v>7</v>
@@ -2421,7 +2421,7 @@
       <c r="D11" s="24"/>
       <c r="E11" s="20"/>
     </row>
-    <row customHeight="1" ht="17" r="12" spans="1:5">
+    <row r="12" ht="17" customHeight="1" spans="1:5">
       <c r="A12" s="28"/>
       <c r="B12" s="29"/>
       <c r="C12" s="30" t="s">
@@ -2436,8 +2436,8 @@
   <mergeCells count="1">
     <mergeCell ref="B3:D3"/>
   </mergeCells>
-  <pageMargins bottom="1" footer="0.25" header="0.25" left="1" right="1" top="1"/>
-  <pageSetup orientation="portrait" paperSize="1" useFirstPageNumber="1"/>
+  <pageMargins left="1" right="1" top="1" bottom="1" header="0.25" footer="0.25"/>
+  <pageSetup paperSize="1" orientation="portrait" useFirstPageNumber="1"/>
   <headerFooter>
     <oddFooter>&amp;C&amp;"Helvetica Neue,Regular"&amp;12&amp;K000000&amp;P</oddFooter>
   </headerFooter>
@@ -2445,26 +2445,26 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Y10"/>
-  <sheetFormatPr customHeight="1" defaultColWidth="9" defaultRowHeight="14.45"/>
+  <dimension ref="A1:X10"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.45" customHeight="1"/>
   <cols>
-    <col min="1" max="1" customWidth="true" style="1" width="9.0" collapsed="true"/>
-    <col min="2" max="2" customWidth="true" style="1" width="14.352380952381" collapsed="true"/>
-    <col min="3" max="4" customWidth="true" style="1" width="17.0" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" style="1" width="9.0" collapsed="true"/>
-    <col min="6" max="6" customWidth="true" style="1" width="88.847619047619" collapsed="true"/>
-    <col min="7" max="7" customWidth="true" style="1" width="34.1714285714286" collapsed="true"/>
-    <col min="8" max="9" customWidth="true" style="1" width="9.0" collapsed="true"/>
-    <col min="10" max="10" customWidth="true" style="1" width="13.5047619047619" collapsed="true"/>
-    <col min="11" max="11" customWidth="true" style="1" width="42.0" collapsed="true"/>
-    <col min="12" max="12" customWidth="true" style="1" width="27.5047619047619" collapsed="true"/>
-    <col min="13" max="18" customWidth="true" style="1" width="73.352380952381" collapsed="true"/>
-    <col min="19" max="257" customWidth="true" style="1" width="9.0" collapsed="true"/>
+    <col min="1" max="1" width="9" style="1" customWidth="1"/>
+    <col min="2" max="2" width="14.3518518518519" style="1" customWidth="1"/>
+    <col min="3" max="4" width="17" style="1" customWidth="1"/>
+    <col min="5" max="5" width="9" style="1" customWidth="1"/>
+    <col min="6" max="6" width="88.8518518518518" style="1" customWidth="1"/>
+    <col min="7" max="7" width="34.1759259259259" style="1" customWidth="1"/>
+    <col min="8" max="9" width="9" style="1" customWidth="1"/>
+    <col min="10" max="10" width="13.5092592592593" style="1" customWidth="1"/>
+    <col min="11" max="11" width="42" style="1" customWidth="1"/>
+    <col min="12" max="12" width="27.5092592592593" style="1" customWidth="1"/>
+    <col min="13" max="18" width="73.3518518518518" style="1" customWidth="1"/>
+    <col min="19" max="257" width="9" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row customHeight="1" ht="13.5" r="1" spans="1:24">
+    <row r="1" ht="13.5" customHeight="1" spans="1:24">
       <c r="A1" s="3" t="s">
         <v>9</v>
       </c>
@@ -2492,19 +2492,19 @@
       <c r="I1" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="J1" s="6" t="s">
+      <c r="J1" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="K1" s="7" t="s">
+      <c r="K1" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="L1" s="7" t="s">
+      <c r="L1" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="M1" s="7" t="s">
+      <c r="M1" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="N1" s="8" t="s">
+      <c r="N1" s="7" t="s">
         <v>22</v>
       </c>
       <c r="O1" s="3" t="s">
@@ -2522,7 +2522,7 @@
       <c r="S1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="T1" s="13" t="s">
+      <c r="T1" s="8" t="s">
         <v>28</v>
       </c>
       <c r="U1" s="1" t="s">
@@ -2538,8 +2538,8 @@
         <v>32</v>
       </c>
     </row>
-    <row customHeight="1" ht="13.5" r="2" spans="1:18">
-      <c r="A2" s="5">
+    <row r="2" ht="13.5" customHeight="1" spans="1:24">
+      <c r="A2" s="9">
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
@@ -2566,34 +2566,34 @@
       <c r="I2" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="J2" s="6" t="s">
+      <c r="J2" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="K2" s="7" t="s">
+      <c r="K2" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="L2" s="7" t="s">
+      <c r="L2" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="M2" s="7" t="s">
+      <c r="M2" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="N2" s="9" t="s">
+      <c r="N2" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="O2" s="10" t="s">
+      <c r="O2" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="P2" s="11"/>
-      <c r="Q2" s="10" t="s">
+      <c r="P2" s="12"/>
+      <c r="Q2" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="R2" s="10" t="s">
+      <c r="R2" s="11" t="s">
         <v>46</v>
       </c>
     </row>
-    <row customHeight="1" ht="13.5" r="3" spans="1:24">
-      <c r="A3" s="5">
+    <row r="3" ht="13.5" customHeight="1" spans="1:24">
+      <c r="A3" s="9">
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
@@ -2620,41 +2620,41 @@
       <c r="I3" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="J3" s="6" t="s">
+      <c r="J3" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="K3" s="7" t="s">
+      <c r="K3" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="L3" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="M3" s="6"/>
+      <c r="N3" s="6"/>
+      <c r="O3" s="6"/>
+      <c r="P3" s="6"/>
+      <c r="Q3" s="6"/>
+      <c r="R3" s="6"/>
+      <c r="S3" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="L3" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="M3" s="7"/>
-      <c r="N3" s="7"/>
-      <c r="O3" s="7"/>
-      <c r="P3" s="7"/>
-      <c r="Q3" s="7"/>
-      <c r="R3" s="7"/>
-      <c r="S3" s="1" t="s">
+      <c r="T3" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="T3" s="14" t="s">
+      <c r="U3" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="U3" s="1" t="s">
+      <c r="V3" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="V3" s="1" t="s">
+      <c r="W3" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="W3" s="1" t="s">
+      <c r="X3" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="X3" s="1" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row customHeight="1" ht="13.5" r="4" spans="1:18">
+    </row>
+    <row r="4" ht="13.5" customHeight="1" spans="1:24">
       <c r="A4" s="4"/>
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
@@ -2665,20 +2665,20 @@
       <c r="H4" s="4"/>
       <c r="I4" s="4"/>
       <c r="J4" s="4"/>
-      <c r="K4" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="L4" s="7" t="s">
+      <c r="K4" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="L4" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="M4" s="12"/>
-      <c r="N4" s="12"/>
-      <c r="O4" s="12"/>
-      <c r="P4" s="12"/>
-      <c r="Q4" s="12"/>
-      <c r="R4" s="12"/>
-    </row>
-    <row customHeight="1" ht="13.5" r="5" spans="1:18">
+      <c r="M4" s="14"/>
+      <c r="N4" s="14"/>
+      <c r="O4" s="14"/>
+      <c r="P4" s="14"/>
+      <c r="Q4" s="14"/>
+      <c r="R4" s="14"/>
+    </row>
+    <row r="5" ht="13.5" customHeight="1" spans="1:24">
       <c r="A5" s="4"/>
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
@@ -2689,7 +2689,7 @@
       <c r="H5" s="4"/>
       <c r="I5" s="4"/>
       <c r="J5" s="4"/>
-      <c r="L5" s="7"/>
+      <c r="L5" s="6"/>
       <c r="M5" s="4"/>
       <c r="N5" s="4"/>
       <c r="O5" s="4"/>
@@ -2697,7 +2697,7 @@
       <c r="Q5" s="4"/>
       <c r="R5" s="4"/>
     </row>
-    <row customHeight="1" ht="13.5" r="6" spans="1:18">
+    <row r="6" ht="13.5" customHeight="1" spans="1:24">
       <c r="A6" s="4"/>
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
@@ -2717,7 +2717,7 @@
       <c r="Q6" s="4"/>
       <c r="R6" s="4"/>
     </row>
-    <row customHeight="1" ht="13.5" r="7" spans="1:18">
+    <row r="7" ht="13.5" customHeight="1" spans="1:24">
       <c r="A7" s="4"/>
       <c r="B7" s="4"/>
       <c r="C7" s="4"/>
@@ -2737,7 +2737,7 @@
       <c r="Q7" s="4"/>
       <c r="R7" s="4"/>
     </row>
-    <row customHeight="1" ht="13.5" r="8" spans="1:18">
+    <row r="8" ht="13.5" customHeight="1" spans="1:24">
       <c r="A8" s="4"/>
       <c r="B8" s="4"/>
       <c r="C8" s="4"/>
@@ -2757,7 +2757,7 @@
       <c r="Q8" s="4"/>
       <c r="R8" s="4"/>
     </row>
-    <row customHeight="1" ht="13.5" r="9" spans="1:18">
+    <row r="9" ht="13.5" customHeight="1" spans="1:24">
       <c r="A9" s="4"/>
       <c r="B9" s="4"/>
       <c r="C9" s="4"/>
@@ -2777,7 +2777,7 @@
       <c r="Q9" s="4"/>
       <c r="R9" s="4"/>
     </row>
-    <row customHeight="1" ht="13.5" r="10" spans="1:18">
+    <row r="10" ht="13.5" customHeight="1" spans="1:24">
       <c r="A10" s="4"/>
       <c r="B10" s="4"/>
       <c r="C10" s="4"/>
@@ -2799,10 +2799,10 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink display="\\10.11.1.158\03. TEST Team\NLB SLO\FileShare\UAT" r:id="rId1" ref="T3" tooltip="\\10.11.1.158\03. TEST Team\NLB SLO\FileShare\UAT"/>
+    <hyperlink ref="T3" r:id="rId1" display="\\10.11.1.158\03. TEST Team\NLB SLO\FileShare\UAT" tooltip="\\10.11.1.158\03. TEST Team\NLB SLO\FileShare\UAT"/>
   </hyperlinks>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-  <pageSetup orientation="portrait" paperSize="1" useFirstPageNumber="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="1" orientation="portrait" useFirstPageNumber="1"/>
   <headerFooter>
     <oddFooter>&amp;C&amp;"Helvetica Neue,Regular"&amp;12&amp;K000000&amp;P</oddFooter>
   </headerFooter>
@@ -2810,20 +2810,20 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F10"/>
-  <sheetFormatPr customHeight="1" defaultColWidth="8.82857142857143" defaultRowHeight="14.45" outlineLevelCol="4"/>
+  <dimension ref="A1:E10"/>
+  <sheetFormatPr defaultColWidth="8.82407407407407" defaultRowHeight="14.45" customHeight="1" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" customWidth="true" style="1" width="12.6761904761905" collapsed="true"/>
-    <col min="2" max="2" customWidth="true" style="1" width="68.352380952381" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="1" width="7.5047619047619" collapsed="true"/>
-    <col min="4" max="4" customWidth="true" style="1" width="11.6761904761905" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" style="1" width="9.67619047619048" collapsed="true"/>
-    <col min="6" max="256" customWidth="true" style="1" width="8.84761904761905" collapsed="true"/>
+    <col min="1" max="1" width="12.6759259259259" style="1" customWidth="1" collapsed="1"/>
+    <col min="2" max="2" width="68.3518518518518" style="1" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="7.50925925925926" style="1" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="11.6759259259259" style="1" customWidth="1" collapsed="1"/>
+    <col min="5" max="5" width="9.67592592592593" style="1" customWidth="1" collapsed="1"/>
+    <col min="6" max="256" width="8.85185185185185" style="1" customWidth="1" collapsed="1"/>
   </cols>
   <sheetData>
-    <row customHeight="1" ht="13.5" r="1" spans="1:5">
+    <row r="1" ht="13.5" customHeight="1" spans="1:5">
       <c r="A1" s="2" t="s">
         <v>13</v>
       </c>
@@ -2840,7 +2840,7 @@
         <v>15</v>
       </c>
     </row>
-    <row customHeight="1" ht="13.5" r="2" spans="1:5">
+    <row r="2" ht="13.5" customHeight="1" spans="1:5">
       <c r="A2" s="3" t="s">
         <v>36</v>
       </c>
@@ -2851,7 +2851,7 @@
       <c r="D2" s="4"/>
       <c r="E2" s="4"/>
     </row>
-    <row customHeight="1" ht="13.5" r="3" spans="1:5">
+    <row r="3" ht="13.5" customHeight="1" spans="1:5">
       <c r="A3" s="3" t="s">
         <v>43</v>
       </c>
@@ -2868,7 +2868,7 @@
         <v>61</v>
       </c>
     </row>
-    <row customHeight="1" ht="13.5" r="4" spans="1:5">
+    <row r="4" ht="13.5" customHeight="1" spans="1:5">
       <c r="A4" s="3" t="s">
         <v>62</v>
       </c>
@@ -2879,9 +2879,9 @@
       <c r="D4" s="4"/>
       <c r="E4" s="4"/>
     </row>
-    <row customHeight="1" ht="13.5" r="5" spans="1:5">
+    <row r="5" ht="13.5" customHeight="1" spans="1:5">
       <c r="A5" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>64</v>
@@ -2890,35 +2890,35 @@
       <c r="D5" s="4"/>
       <c r="E5" s="4"/>
     </row>
-    <row customHeight="1" ht="13.5" r="6" spans="1:5">
+    <row r="6" ht="13.5" customHeight="1" spans="1:5">
       <c r="A6" s="4"/>
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
       <c r="D6" s="4"/>
       <c r="E6" s="4"/>
     </row>
-    <row customHeight="1" ht="13.5" r="7" spans="1:5">
+    <row r="7" ht="13.5" customHeight="1" spans="1:5">
       <c r="A7" s="4"/>
       <c r="B7" s="4"/>
       <c r="C7" s="4"/>
       <c r="D7" s="4"/>
       <c r="E7" s="4"/>
     </row>
-    <row customHeight="1" ht="13.5" r="8" spans="1:5">
+    <row r="8" ht="13.5" customHeight="1" spans="1:5">
       <c r="A8" s="4"/>
       <c r="B8" s="4"/>
       <c r="C8" s="4"/>
       <c r="D8" s="4"/>
       <c r="E8" s="4"/>
     </row>
-    <row customHeight="1" ht="13.5" r="9" spans="1:5">
+    <row r="9" ht="13.5" customHeight="1" spans="1:5">
       <c r="A9" s="4"/>
       <c r="B9" s="4"/>
       <c r="C9" s="4"/>
       <c r="D9" s="4"/>
       <c r="E9" s="4"/>
     </row>
-    <row customHeight="1" ht="13.5" r="10" spans="1:5">
+    <row r="10" ht="13.5" customHeight="1" spans="1:5">
       <c r="A10" s="4"/>
       <c r="B10" s="4"/>
       <c r="C10" s="4"/>
@@ -2926,8 +2926,8 @@
       <c r="E10" s="4"/>
     </row>
   </sheetData>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
-  <pageSetup orientation="portrait" paperSize="1" useFirstPageNumber="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="1" orientation="portrait" useFirstPageNumber="1"/>
   <headerFooter>
     <oddFooter>&amp;C&amp;"Helvetica Neue,Regular"&amp;12&amp;K000000&amp;P</oddFooter>
   </headerFooter>

--- a/testdata/configuration_environment.xlsx
+++ b/testdata/configuration_environment.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9000" activeTab="1"/>
+    <workbookView activeTab="1" windowHeight="9000" windowWidth="23040"/>
   </bookViews>
   <sheets>
-    <sheet name="Export Summary" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
-    <sheet name="Conn" sheetId="3" r:id="rId3"/>
+    <sheet name="Export Summary" r:id="rId1" sheetId="1"/>
+    <sheet name="Sheet1" r:id="rId2" sheetId="2"/>
+    <sheet name="Conn" r:id="rId3" sheetId="3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="65">
   <si>
     <t>This document was exported from Numbers. Each table was converted to an Excel worksheet. All other objects on each Numbers sheet were placed on separate worksheets. Please be aware that formula calculations may differ in Excel.</t>
   </si>
@@ -944,263 +944,263 @@
     </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="16" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="19" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="20" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="19" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="22" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="23" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0" borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf applyAlignment="0" applyBorder="0" applyFill="0" applyFont="0" applyProtection="0" borderId="0" fillId="0" fontId="2" numFmtId="176">
+      <alignment vertical="center"/>
+    </xf>
+    <xf applyAlignment="0" applyBorder="0" applyFill="0" applyFont="0" applyProtection="0" borderId="0" fillId="0" fontId="2" numFmtId="44">
+      <alignment vertical="center"/>
+    </xf>
+    <xf applyAlignment="0" applyBorder="0" applyFill="0" applyFont="0" applyProtection="0" borderId="0" fillId="0" fontId="2" numFmtId="9">
+      <alignment vertical="center"/>
+    </xf>
+    <xf applyAlignment="0" applyBorder="0" applyFill="0" applyFont="0" applyProtection="0" borderId="0" fillId="0" fontId="2" numFmtId="177">
+      <alignment vertical="center"/>
+    </xf>
+    <xf applyAlignment="0" applyBorder="0" applyFill="0" applyFont="0" applyProtection="0" borderId="0" fillId="0" fontId="2" numFmtId="42">
+      <alignment vertical="center"/>
+    </xf>
+    <xf applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0" borderId="0" fillId="0" fontId="3" numFmtId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0" borderId="0" fillId="0" fontId="7" numFmtId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf applyAlignment="0" applyFont="0" applyNumberFormat="0" applyProtection="0" borderId="16" fillId="5" fontId="2" numFmtId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0" borderId="0" fillId="0" fontId="8" numFmtId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0" borderId="0" fillId="0" fontId="9" numFmtId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0" borderId="0" fillId="0" fontId="10" numFmtId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0" borderId="17" fillId="0" fontId="11" numFmtId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0" borderId="17" fillId="0" fontId="12" numFmtId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0" borderId="18" fillId="0" fontId="13" numFmtId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0" borderId="0" fillId="0" fontId="13" numFmtId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf applyAlignment="0" applyNumberFormat="0" applyProtection="0" borderId="19" fillId="6" fontId="14" numFmtId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf applyAlignment="0" applyNumberFormat="0" applyProtection="0" borderId="20" fillId="7" fontId="15" numFmtId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf applyAlignment="0" applyNumberFormat="0" applyProtection="0" borderId="19" fillId="7" fontId="16" numFmtId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf applyAlignment="0" applyNumberFormat="0" applyProtection="0" borderId="21" fillId="8" fontId="17" numFmtId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0" borderId="22" fillId="0" fontId="18" numFmtId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0" borderId="23" fillId="0" fontId="19" numFmtId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0" borderId="0" fillId="9" fontId="20" numFmtId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0" borderId="0" fillId="10" fontId="21" numFmtId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0" borderId="0" fillId="11" fontId="22" numFmtId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0" borderId="0" fillId="12" fontId="23" numFmtId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0" borderId="0" fillId="13" fontId="24" numFmtId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0" borderId="0" fillId="14" fontId="24" numFmtId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0" borderId="0" fillId="15" fontId="23" numFmtId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0" borderId="0" fillId="16" fontId="23" numFmtId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0" borderId="0" fillId="17" fontId="24" numFmtId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0" borderId="0" fillId="18" fontId="24" numFmtId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0" borderId="0" fillId="19" fontId="23" numFmtId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0" borderId="0" fillId="20" fontId="23" numFmtId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0" borderId="0" fillId="21" fontId="24" numFmtId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0" borderId="0" fillId="22" fontId="24" numFmtId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0" borderId="0" fillId="23" fontId="23" numFmtId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0" borderId="0" fillId="24" fontId="23" numFmtId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0" borderId="0" fillId="25" fontId="24" numFmtId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0" borderId="0" fillId="26" fontId="24" numFmtId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0" borderId="0" fillId="27" fontId="23" numFmtId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0" borderId="0" fillId="28" fontId="23" numFmtId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0" borderId="0" fillId="29" fontId="24" numFmtId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0" borderId="0" fillId="30" fontId="24" numFmtId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0" borderId="0" fillId="31" fontId="23" numFmtId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0" borderId="0" fillId="32" fontId="23" numFmtId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0" borderId="0" fillId="33" fontId="24" numFmtId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0" borderId="0" fillId="34" fontId="24" numFmtId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0" borderId="0" fillId="35" fontId="23" numFmtId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="33">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf applyAlignment="1" applyFont="1" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0"/>
+    <xf applyAlignment="1" applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0"/>
+    <xf applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1" borderId="1" fillId="2" fontId="1" numFmtId="49" xfId="0"/>
+    <xf applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1" borderId="1" fillId="2" fontId="0" numFmtId="49" xfId="0"/>
+    <xf applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" borderId="1" fillId="2" fontId="0" numFmtId="0" xfId="0"/>
+    <xf applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1" borderId="2" fillId="2" fontId="0" numFmtId="49" xfId="0"/>
+    <xf applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1" borderId="3" fillId="2" fontId="0" numFmtId="49" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1" borderId="4" fillId="2" fontId="0" numFmtId="49" xfId="0"/>
+    <xf applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1" applyProtection="1" borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1" borderId="1" fillId="2" fontId="0" numFmtId="0" xfId="0"/>
+    <xf applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1" borderId="5" fillId="2" fontId="0" numFmtId="49" xfId="0"/>
+    <xf applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1" borderId="6" fillId="2" fontId="0" numFmtId="49" xfId="0"/>
+    <xf applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" borderId="6" fillId="2" fontId="0" numFmtId="0" xfId="0"/>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" borderId="7" fillId="2" fontId="0" numFmtId="0" xfId="0"/>
+    <xf applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" borderId="8" fillId="2" fontId="0" numFmtId="0" xfId="0"/>
+    <xf applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" borderId="9" fillId="2" fontId="0" numFmtId="0" xfId="0"/>
+    <xf applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" borderId="10" fillId="2" fontId="0" numFmtId="0" xfId="0"/>
+    <xf applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" borderId="11" fillId="2" fontId="0" numFmtId="0" xfId="0"/>
+    <xf applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" borderId="0" fillId="2" fontId="0" numFmtId="0" xfId="0"/>
+    <xf applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" borderId="12" fillId="2" fontId="0" numFmtId="0" xfId="0"/>
+    <xf applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1" borderId="0" fillId="2" fontId="4" numFmtId="49" xfId="0">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1" borderId="0" fillId="2" fontId="5" numFmtId="49" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1" borderId="0" fillId="3" fontId="4" numFmtId="49" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" borderId="0" fillId="3" fontId="4" numFmtId="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" borderId="0" fillId="4" fontId="4" numFmtId="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1" borderId="0" fillId="4" fontId="4" numFmtId="49" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1" borderId="0" fillId="4" fontId="6" numFmtId="49" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" borderId="13" fillId="2" fontId="0" numFmtId="0" xfId="0"/>
+    <xf applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" borderId="14" fillId="4" fontId="4" numFmtId="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="4" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1" borderId="14" fillId="4" fontId="4" numFmtId="49" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="4" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1" borderId="14" fillId="4" fontId="6" numFmtId="49" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" borderId="15" fillId="2" fontId="0" numFmtId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="49">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="1" builtinId="3"/>
-    <cellStyle name="Currency" xfId="2" builtinId="4"/>
-    <cellStyle name="Percent" xfId="3" builtinId="5"/>
-    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
-    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
-    <cellStyle name="Link" xfId="6" builtinId="8"/>
-    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
-    <cellStyle name="Note" xfId="8" builtinId="10"/>
-    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
-    <cellStyle name="Title" xfId="10" builtinId="15"/>
-    <cellStyle name="Explanatory Text" xfId="11" builtinId="53"/>
-    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
-    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
-    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
-    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
-    <cellStyle name="Input" xfId="16" builtinId="20"/>
-    <cellStyle name="Output" xfId="17" builtinId="21"/>
-    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
-    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
-    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
-    <cellStyle name="Total" xfId="21" builtinId="25"/>
-    <cellStyle name="Good" xfId="22" builtinId="26"/>
-    <cellStyle name="Bad" xfId="23" builtinId="27"/>
-    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
-    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
-    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
-    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
-    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
-    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
-    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
+    <cellStyle builtinId="0" name="Normal" xfId="0"/>
+    <cellStyle builtinId="3" name="Comma" xfId="1"/>
+    <cellStyle builtinId="4" name="Currency" xfId="2"/>
+    <cellStyle builtinId="5" name="Percent" xfId="3"/>
+    <cellStyle builtinId="6" name="Comma [0]" xfId="4"/>
+    <cellStyle builtinId="7" name="Currency [0]" xfId="5"/>
+    <cellStyle builtinId="8" name="Link" xfId="6"/>
+    <cellStyle builtinId="9" name="Followed Hyperlink" xfId="7"/>
+    <cellStyle builtinId="10" name="Note" xfId="8"/>
+    <cellStyle builtinId="11" name="Warning Text" xfId="9"/>
+    <cellStyle builtinId="15" name="Title" xfId="10"/>
+    <cellStyle builtinId="53" name="Explanatory Text" xfId="11"/>
+    <cellStyle builtinId="16" name="Heading 1" xfId="12"/>
+    <cellStyle builtinId="17" name="Heading 2" xfId="13"/>
+    <cellStyle builtinId="18" name="Heading 3" xfId="14"/>
+    <cellStyle builtinId="19" name="Heading 4" xfId="15"/>
+    <cellStyle builtinId="20" name="Input" xfId="16"/>
+    <cellStyle builtinId="21" name="Output" xfId="17"/>
+    <cellStyle builtinId="22" name="Calculation" xfId="18"/>
+    <cellStyle builtinId="23" name="Check Cell" xfId="19"/>
+    <cellStyle builtinId="24" name="Linked Cell" xfId="20"/>
+    <cellStyle builtinId="25" name="Total" xfId="21"/>
+    <cellStyle builtinId="26" name="Good" xfId="22"/>
+    <cellStyle builtinId="27" name="Bad" xfId="23"/>
+    <cellStyle builtinId="28" name="Neutral" xfId="24"/>
+    <cellStyle builtinId="29" name="Accent1" xfId="25"/>
+    <cellStyle builtinId="30" name="20% - Accent1" xfId="26"/>
+    <cellStyle builtinId="31" name="40% - Accent1" xfId="27"/>
+    <cellStyle builtinId="32" name="60% - Accent1" xfId="28"/>
+    <cellStyle builtinId="33" name="Accent2" xfId="29"/>
+    <cellStyle builtinId="34" name="20% - Accent2" xfId="30"/>
+    <cellStyle builtinId="35" name="40% - Accent2" xfId="31"/>
+    <cellStyle builtinId="36" name="60% - Accent2" xfId="32"/>
+    <cellStyle builtinId="37" name="Accent3" xfId="33"/>
+    <cellStyle builtinId="38" name="20% - Accent3" xfId="34"/>
+    <cellStyle builtinId="39" name="40% - Accent3" xfId="35"/>
+    <cellStyle builtinId="40" name="60% - Accent3" xfId="36"/>
+    <cellStyle builtinId="41" name="Accent4" xfId="37"/>
+    <cellStyle builtinId="42" name="20% - Accent4" xfId="38"/>
+    <cellStyle builtinId="43" name="40% - Accent4" xfId="39"/>
+    <cellStyle builtinId="44" name="60% - Accent4" xfId="40"/>
+    <cellStyle builtinId="45" name="Accent5" xfId="41"/>
+    <cellStyle builtinId="46" name="20% - Accent5" xfId="42"/>
+    <cellStyle builtinId="47" name="40% - Accent5" xfId="43"/>
+    <cellStyle builtinId="48" name="60% - Accent5" xfId="44"/>
+    <cellStyle builtinId="49" name="Accent6" xfId="45"/>
+    <cellStyle builtinId="50" name="20% - Accent6" xfId="46"/>
+    <cellStyle builtinId="51" name="40% - Accent6" xfId="47"/>
+    <cellStyle builtinId="52" name="60% - Accent6" xfId="48"/>
   </cellStyles>
   <tableStyles count="0"/>
   <colors>
@@ -1381,7 +1381,7 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cap="flat" cmpd="sng" w="9525">
           <a:solidFill>
             <a:schemeClr val="phClr">
               <a:shade val="95000"/>
@@ -1390,13 +1390,13 @@
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cap="flat" cmpd="sng" w="25400">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cap="flat" cmpd="sng" w="38100">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -1441,7 +1441,7 @@
             </a:gs>
           </a:gsLst>
           <a:path path="circle">
-            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+            <a:fillToRect b="180000" l="50000" r="50000" t="-80000"/>
           </a:path>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
@@ -1460,7 +1460,7 @@
             </a:gs>
           </a:gsLst>
           <a:path path="circle">
-            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+            <a:fillToRect b="50000" l="50000" r="50000" t="50000"/>
           </a:path>
         </a:gradFill>
       </a:bgFillStyleLst>
@@ -1472,7 +1472,7 @@
         <a:solidFill>
           <a:srgbClr val="FFFFFF"/>
         </a:solidFill>
-        <a:ln w="25400" cap="flat">
+        <a:ln cap="flat" w="25400">
           <a:solidFill>
             <a:schemeClr val="accent1"/>
           </a:solidFill>
@@ -1480,11 +1480,11 @@
           <a:round/>
         </a:ln>
       </a:spPr>
-      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="45718" tIns="45718" rIns="45718" bIns="45718" numCol="1" spcCol="38100" rtlCol="0" anchor="ctr" upright="0">
+      <a:bodyPr anchor="ctr" bIns="45718" horzOverflow="overflow" lIns="45718" numCol="1" rIns="45718" rot="0" rtlCol="0" spcCol="38100" spcFirstLastPara="1" tIns="45718" upright="0" vert="horz" vertOverflow="overflow" wrap="square">
         <a:spAutoFit/>
       </a:bodyPr>
       <a:lstStyle>
-        <a:defPPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="0" hangingPunct="0">
+        <a:defPPr algn="l" defTabSz="914400" fontAlgn="auto" hangingPunct="0" indent="0" latinLnBrk="0" marL="0" marR="0" rtl="0">
           <a:lnSpc>
             <a:spcPct val="100000"/>
           </a:lnSpc>
@@ -1498,7 +1498,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr kumimoji="0" sz="1100" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
+          <a:defRPr b="0" baseline="0" cap="none" i="0" kumimoji="0" normalizeH="0" spc="0" strike="noStrike" sz="1100" u="none">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1513,7 +1513,7 @@
             <a:sym typeface="Helvetica Neue"/>
           </a:defRPr>
         </a:defPPr>
-        <a:lvl1pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="1" hangingPunct="0">
+        <a:lvl1pPr algn="l" defTabSz="914400" fontAlgn="auto" hangingPunct="0" indent="0" latinLnBrk="1" marL="0" marR="0" rtl="0">
           <a:lnSpc>
             <a:spcPct val="100000"/>
           </a:lnSpc>
@@ -1527,7 +1527,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
+          <a:defRPr b="0" baseline="0" cap="none" i="0" kumimoji="0" normalizeH="0" spc="0" strike="noStrike" sz="1800" u="none">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1538,7 +1538,7 @@
             <a:uFillTx/>
           </a:defRPr>
         </a:lvl1pPr>
-        <a:lvl2pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="1" hangingPunct="0">
+        <a:lvl2pPr algn="l" defTabSz="914400" fontAlgn="auto" hangingPunct="0" indent="0" latinLnBrk="1" marL="0" marR="0" rtl="0">
           <a:lnSpc>
             <a:spcPct val="100000"/>
           </a:lnSpc>
@@ -1552,7 +1552,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
+          <a:defRPr b="0" baseline="0" cap="none" i="0" kumimoji="0" normalizeH="0" spc="0" strike="noStrike" sz="1800" u="none">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1563,7 +1563,7 @@
             <a:uFillTx/>
           </a:defRPr>
         </a:lvl2pPr>
-        <a:lvl3pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="1" hangingPunct="0">
+        <a:lvl3pPr algn="l" defTabSz="914400" fontAlgn="auto" hangingPunct="0" indent="0" latinLnBrk="1" marL="0" marR="0" rtl="0">
           <a:lnSpc>
             <a:spcPct val="100000"/>
           </a:lnSpc>
@@ -1577,7 +1577,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
+          <a:defRPr b="0" baseline="0" cap="none" i="0" kumimoji="0" normalizeH="0" spc="0" strike="noStrike" sz="1800" u="none">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1588,7 +1588,7 @@
             <a:uFillTx/>
           </a:defRPr>
         </a:lvl3pPr>
-        <a:lvl4pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="1" hangingPunct="0">
+        <a:lvl4pPr algn="l" defTabSz="914400" fontAlgn="auto" hangingPunct="0" indent="0" latinLnBrk="1" marL="0" marR="0" rtl="0">
           <a:lnSpc>
             <a:spcPct val="100000"/>
           </a:lnSpc>
@@ -1602,7 +1602,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
+          <a:defRPr b="0" baseline="0" cap="none" i="0" kumimoji="0" normalizeH="0" spc="0" strike="noStrike" sz="1800" u="none">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1613,7 +1613,7 @@
             <a:uFillTx/>
           </a:defRPr>
         </a:lvl4pPr>
-        <a:lvl5pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="1" hangingPunct="0">
+        <a:lvl5pPr algn="l" defTabSz="914400" fontAlgn="auto" hangingPunct="0" indent="0" latinLnBrk="1" marL="0" marR="0" rtl="0">
           <a:lnSpc>
             <a:spcPct val="100000"/>
           </a:lnSpc>
@@ -1627,7 +1627,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
+          <a:defRPr b="0" baseline="0" cap="none" i="0" kumimoji="0" normalizeH="0" spc="0" strike="noStrike" sz="1800" u="none">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1638,7 +1638,7 @@
             <a:uFillTx/>
           </a:defRPr>
         </a:lvl5pPr>
-        <a:lvl6pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="1" hangingPunct="0">
+        <a:lvl6pPr algn="l" defTabSz="914400" fontAlgn="auto" hangingPunct="0" indent="0" latinLnBrk="1" marL="0" marR="0" rtl="0">
           <a:lnSpc>
             <a:spcPct val="100000"/>
           </a:lnSpc>
@@ -1652,7 +1652,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
+          <a:defRPr b="0" baseline="0" cap="none" i="0" kumimoji="0" normalizeH="0" spc="0" strike="noStrike" sz="1800" u="none">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1663,7 +1663,7 @@
             <a:uFillTx/>
           </a:defRPr>
         </a:lvl6pPr>
-        <a:lvl7pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="1" hangingPunct="0">
+        <a:lvl7pPr algn="l" defTabSz="914400" fontAlgn="auto" hangingPunct="0" indent="0" latinLnBrk="1" marL="0" marR="0" rtl="0">
           <a:lnSpc>
             <a:spcPct val="100000"/>
           </a:lnSpc>
@@ -1677,7 +1677,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
+          <a:defRPr b="0" baseline="0" cap="none" i="0" kumimoji="0" normalizeH="0" spc="0" strike="noStrike" sz="1800" u="none">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1688,7 +1688,7 @@
             <a:uFillTx/>
           </a:defRPr>
         </a:lvl7pPr>
-        <a:lvl8pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="1" hangingPunct="0">
+        <a:lvl8pPr algn="l" defTabSz="914400" fontAlgn="auto" hangingPunct="0" indent="0" latinLnBrk="1" marL="0" marR="0" rtl="0">
           <a:lnSpc>
             <a:spcPct val="100000"/>
           </a:lnSpc>
@@ -1702,7 +1702,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
+          <a:defRPr b="0" baseline="0" cap="none" i="0" kumimoji="0" normalizeH="0" spc="0" strike="noStrike" sz="1800" u="none">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1713,7 +1713,7 @@
             <a:uFillTx/>
           </a:defRPr>
         </a:lvl8pPr>
-        <a:lvl9pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="1" hangingPunct="0">
+        <a:lvl9pPr algn="l" defTabSz="914400" fontAlgn="auto" hangingPunct="0" indent="0" latinLnBrk="1" marL="0" marR="0" rtl="0">
           <a:lnSpc>
             <a:spcPct val="100000"/>
           </a:lnSpc>
@@ -1727,7 +1727,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
+          <a:defRPr b="0" baseline="0" cap="none" i="0" kumimoji="0" normalizeH="0" spc="0" strike="noStrike" sz="1800" u="none">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1755,7 +1755,7 @@
     <a:lnDef>
       <a:spPr>
         <a:noFill/>
-        <a:ln w="25400" cap="flat">
+        <a:ln cap="flat" w="25400">
           <a:solidFill>
             <a:schemeClr val="accent1"/>
           </a:solidFill>
@@ -1763,11 +1763,11 @@
           <a:round/>
         </a:ln>
       </a:spPr>
-      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="91439" tIns="45719" rIns="91439" bIns="45719" numCol="1" spcCol="38100" rtlCol="0" anchor="t" upright="0">
+      <a:bodyPr anchor="t" bIns="45719" horzOverflow="overflow" lIns="91439" numCol="1" rIns="91439" rot="0" rtlCol="0" spcCol="38100" spcFirstLastPara="1" tIns="45719" upright="0" vert="horz" vertOverflow="overflow" wrap="square">
         <a:noAutofit/>
       </a:bodyPr>
       <a:lstStyle>
-        <a:defPPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="1" hangingPunct="0">
+        <a:defPPr algn="l" defTabSz="914400" fontAlgn="auto" hangingPunct="0" indent="0" latinLnBrk="1" marL="0" marR="0" rtl="0">
           <a:lnSpc>
             <a:spcPct val="100000"/>
           </a:lnSpc>
@@ -1781,7 +1781,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
+          <a:defRPr b="0" baseline="0" cap="none" i="0" kumimoji="0" normalizeH="0" spc="0" strike="noStrike" sz="1800" u="none">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1792,7 +1792,7 @@
             <a:uFillTx/>
           </a:defRPr>
         </a:defPPr>
-        <a:lvl1pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="1" hangingPunct="0">
+        <a:lvl1pPr algn="l" defTabSz="914400" fontAlgn="auto" hangingPunct="0" indent="0" latinLnBrk="1" marL="0" marR="0" rtl="0">
           <a:lnSpc>
             <a:spcPct val="100000"/>
           </a:lnSpc>
@@ -1806,7 +1806,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
+          <a:defRPr b="0" baseline="0" cap="none" i="0" kumimoji="0" normalizeH="0" spc="0" strike="noStrike" sz="1800" u="none">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1817,7 +1817,7 @@
             <a:uFillTx/>
           </a:defRPr>
         </a:lvl1pPr>
-        <a:lvl2pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="1" hangingPunct="0">
+        <a:lvl2pPr algn="l" defTabSz="914400" fontAlgn="auto" hangingPunct="0" indent="0" latinLnBrk="1" marL="0" marR="0" rtl="0">
           <a:lnSpc>
             <a:spcPct val="100000"/>
           </a:lnSpc>
@@ -1831,7 +1831,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
+          <a:defRPr b="0" baseline="0" cap="none" i="0" kumimoji="0" normalizeH="0" spc="0" strike="noStrike" sz="1800" u="none">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1842,7 +1842,7 @@
             <a:uFillTx/>
           </a:defRPr>
         </a:lvl2pPr>
-        <a:lvl3pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="1" hangingPunct="0">
+        <a:lvl3pPr algn="l" defTabSz="914400" fontAlgn="auto" hangingPunct="0" indent="0" latinLnBrk="1" marL="0" marR="0" rtl="0">
           <a:lnSpc>
             <a:spcPct val="100000"/>
           </a:lnSpc>
@@ -1856,7 +1856,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
+          <a:defRPr b="0" baseline="0" cap="none" i="0" kumimoji="0" normalizeH="0" spc="0" strike="noStrike" sz="1800" u="none">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1867,7 +1867,7 @@
             <a:uFillTx/>
           </a:defRPr>
         </a:lvl3pPr>
-        <a:lvl4pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="1" hangingPunct="0">
+        <a:lvl4pPr algn="l" defTabSz="914400" fontAlgn="auto" hangingPunct="0" indent="0" latinLnBrk="1" marL="0" marR="0" rtl="0">
           <a:lnSpc>
             <a:spcPct val="100000"/>
           </a:lnSpc>
@@ -1881,7 +1881,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
+          <a:defRPr b="0" baseline="0" cap="none" i="0" kumimoji="0" normalizeH="0" spc="0" strike="noStrike" sz="1800" u="none">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1892,7 +1892,7 @@
             <a:uFillTx/>
           </a:defRPr>
         </a:lvl4pPr>
-        <a:lvl5pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="1" hangingPunct="0">
+        <a:lvl5pPr algn="l" defTabSz="914400" fontAlgn="auto" hangingPunct="0" indent="0" latinLnBrk="1" marL="0" marR="0" rtl="0">
           <a:lnSpc>
             <a:spcPct val="100000"/>
           </a:lnSpc>
@@ -1906,7 +1906,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
+          <a:defRPr b="0" baseline="0" cap="none" i="0" kumimoji="0" normalizeH="0" spc="0" strike="noStrike" sz="1800" u="none">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1917,7 +1917,7 @@
             <a:uFillTx/>
           </a:defRPr>
         </a:lvl5pPr>
-        <a:lvl6pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="1" hangingPunct="0">
+        <a:lvl6pPr algn="l" defTabSz="914400" fontAlgn="auto" hangingPunct="0" indent="0" latinLnBrk="1" marL="0" marR="0" rtl="0">
           <a:lnSpc>
             <a:spcPct val="100000"/>
           </a:lnSpc>
@@ -1931,7 +1931,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
+          <a:defRPr b="0" baseline="0" cap="none" i="0" kumimoji="0" normalizeH="0" spc="0" strike="noStrike" sz="1800" u="none">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1942,7 +1942,7 @@
             <a:uFillTx/>
           </a:defRPr>
         </a:lvl6pPr>
-        <a:lvl7pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="1" hangingPunct="0">
+        <a:lvl7pPr algn="l" defTabSz="914400" fontAlgn="auto" hangingPunct="0" indent="0" latinLnBrk="1" marL="0" marR="0" rtl="0">
           <a:lnSpc>
             <a:spcPct val="100000"/>
           </a:lnSpc>
@@ -1956,7 +1956,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
+          <a:defRPr b="0" baseline="0" cap="none" i="0" kumimoji="0" normalizeH="0" spc="0" strike="noStrike" sz="1800" u="none">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1967,7 +1967,7 @@
             <a:uFillTx/>
           </a:defRPr>
         </a:lvl7pPr>
-        <a:lvl8pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="1" hangingPunct="0">
+        <a:lvl8pPr algn="l" defTabSz="914400" fontAlgn="auto" hangingPunct="0" indent="0" latinLnBrk="1" marL="0" marR="0" rtl="0">
           <a:lnSpc>
             <a:spcPct val="100000"/>
           </a:lnSpc>
@@ -1981,7 +1981,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
+          <a:defRPr b="0" baseline="0" cap="none" i="0" kumimoji="0" normalizeH="0" spc="0" strike="noStrike" sz="1800" u="none">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1992,7 +1992,7 @@
             <a:uFillTx/>
           </a:defRPr>
         </a:lvl8pPr>
-        <a:lvl9pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="1" hangingPunct="0">
+        <a:lvl9pPr algn="l" defTabSz="914400" fontAlgn="auto" hangingPunct="0" indent="0" latinLnBrk="1" marL="0" marR="0" rtl="0">
           <a:lnSpc>
             <a:spcPct val="100000"/>
           </a:lnSpc>
@@ -2006,7 +2006,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
+          <a:defRPr b="0" baseline="0" cap="none" i="0" kumimoji="0" normalizeH="0" spc="0" strike="noStrike" sz="1800" u="none">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -2034,16 +2034,16 @@
     <a:txDef>
       <a:spPr>
         <a:noFill/>
-        <a:ln w="12700" cap="flat">
+        <a:ln cap="flat" w="12700">
           <a:noFill/>
           <a:miter lim="400000"/>
         </a:ln>
       </a:spPr>
-      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="45718" tIns="45718" rIns="45718" bIns="45718" numCol="1" spcCol="38100" rtlCol="0" anchor="t" upright="0">
+      <a:bodyPr anchor="t" bIns="45718" horzOverflow="overflow" lIns="45718" numCol="1" rIns="45718" rot="0" rtlCol="0" spcCol="38100" spcFirstLastPara="1" tIns="45718" upright="0" vert="horz" vertOverflow="overflow" wrap="square">
         <a:spAutoFit/>
       </a:bodyPr>
       <a:lstStyle>
-        <a:defPPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="0" hangingPunct="0">
+        <a:defPPr algn="l" defTabSz="914400" fontAlgn="auto" hangingPunct="0" indent="0" latinLnBrk="0" marL="0" marR="0" rtl="0">
           <a:lnSpc>
             <a:spcPct val="100000"/>
           </a:lnSpc>
@@ -2057,7 +2057,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr kumimoji="0" sz="1100" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
+          <a:defRPr b="0" baseline="0" cap="none" i="0" kumimoji="0" normalizeH="0" spc="0" strike="noStrike" sz="1100" u="none">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -2072,7 +2072,7 @@
             <a:sym typeface="Helvetica Neue"/>
           </a:defRPr>
         </a:defPPr>
-        <a:lvl1pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="1" hangingPunct="0">
+        <a:lvl1pPr algn="l" defTabSz="914400" fontAlgn="auto" hangingPunct="0" indent="0" latinLnBrk="1" marL="0" marR="0" rtl="0">
           <a:lnSpc>
             <a:spcPct val="100000"/>
           </a:lnSpc>
@@ -2086,7 +2086,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
+          <a:defRPr b="0" baseline="0" cap="none" i="0" kumimoji="0" normalizeH="0" spc="0" strike="noStrike" sz="1800" u="none">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -2097,7 +2097,7 @@
             <a:uFillTx/>
           </a:defRPr>
         </a:lvl1pPr>
-        <a:lvl2pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="1" hangingPunct="0">
+        <a:lvl2pPr algn="l" defTabSz="914400" fontAlgn="auto" hangingPunct="0" indent="0" latinLnBrk="1" marL="0" marR="0" rtl="0">
           <a:lnSpc>
             <a:spcPct val="100000"/>
           </a:lnSpc>
@@ -2111,7 +2111,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
+          <a:defRPr b="0" baseline="0" cap="none" i="0" kumimoji="0" normalizeH="0" spc="0" strike="noStrike" sz="1800" u="none">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -2122,7 +2122,7 @@
             <a:uFillTx/>
           </a:defRPr>
         </a:lvl2pPr>
-        <a:lvl3pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="1" hangingPunct="0">
+        <a:lvl3pPr algn="l" defTabSz="914400" fontAlgn="auto" hangingPunct="0" indent="0" latinLnBrk="1" marL="0" marR="0" rtl="0">
           <a:lnSpc>
             <a:spcPct val="100000"/>
           </a:lnSpc>
@@ -2136,7 +2136,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
+          <a:defRPr b="0" baseline="0" cap="none" i="0" kumimoji="0" normalizeH="0" spc="0" strike="noStrike" sz="1800" u="none">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -2147,7 +2147,7 @@
             <a:uFillTx/>
           </a:defRPr>
         </a:lvl3pPr>
-        <a:lvl4pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="1" hangingPunct="0">
+        <a:lvl4pPr algn="l" defTabSz="914400" fontAlgn="auto" hangingPunct="0" indent="0" latinLnBrk="1" marL="0" marR="0" rtl="0">
           <a:lnSpc>
             <a:spcPct val="100000"/>
           </a:lnSpc>
@@ -2161,7 +2161,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
+          <a:defRPr b="0" baseline="0" cap="none" i="0" kumimoji="0" normalizeH="0" spc="0" strike="noStrike" sz="1800" u="none">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -2172,7 +2172,7 @@
             <a:uFillTx/>
           </a:defRPr>
         </a:lvl4pPr>
-        <a:lvl5pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="1" hangingPunct="0">
+        <a:lvl5pPr algn="l" defTabSz="914400" fontAlgn="auto" hangingPunct="0" indent="0" latinLnBrk="1" marL="0" marR="0" rtl="0">
           <a:lnSpc>
             <a:spcPct val="100000"/>
           </a:lnSpc>
@@ -2186,7 +2186,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
+          <a:defRPr b="0" baseline="0" cap="none" i="0" kumimoji="0" normalizeH="0" spc="0" strike="noStrike" sz="1800" u="none">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -2197,7 +2197,7 @@
             <a:uFillTx/>
           </a:defRPr>
         </a:lvl5pPr>
-        <a:lvl6pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="1" hangingPunct="0">
+        <a:lvl6pPr algn="l" defTabSz="914400" fontAlgn="auto" hangingPunct="0" indent="0" latinLnBrk="1" marL="0" marR="0" rtl="0">
           <a:lnSpc>
             <a:spcPct val="100000"/>
           </a:lnSpc>
@@ -2211,7 +2211,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
+          <a:defRPr b="0" baseline="0" cap="none" i="0" kumimoji="0" normalizeH="0" spc="0" strike="noStrike" sz="1800" u="none">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -2222,7 +2222,7 @@
             <a:uFillTx/>
           </a:defRPr>
         </a:lvl6pPr>
-        <a:lvl7pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="1" hangingPunct="0">
+        <a:lvl7pPr algn="l" defTabSz="914400" fontAlgn="auto" hangingPunct="0" indent="0" latinLnBrk="1" marL="0" marR="0" rtl="0">
           <a:lnSpc>
             <a:spcPct val="100000"/>
           </a:lnSpc>
@@ -2236,7 +2236,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
+          <a:defRPr b="0" baseline="0" cap="none" i="0" kumimoji="0" normalizeH="0" spc="0" strike="noStrike" sz="1800" u="none">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -2247,7 +2247,7 @@
             <a:uFillTx/>
           </a:defRPr>
         </a:lvl7pPr>
-        <a:lvl8pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="1" hangingPunct="0">
+        <a:lvl8pPr algn="l" defTabSz="914400" fontAlgn="auto" hangingPunct="0" indent="0" latinLnBrk="1" marL="0" marR="0" rtl="0">
           <a:lnSpc>
             <a:spcPct val="100000"/>
           </a:lnSpc>
@@ -2261,7 +2261,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
+          <a:defRPr b="0" baseline="0" cap="none" i="0" kumimoji="0" normalizeH="0" spc="0" strike="noStrike" sz="1800" u="none">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -2272,7 +2272,7 @@
             <a:uFillTx/>
           </a:defRPr>
         </a:lvl8pPr>
-        <a:lvl9pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="1" hangingPunct="0">
+        <a:lvl9pPr algn="l" defTabSz="914400" fontAlgn="auto" hangingPunct="0" indent="0" latinLnBrk="1" marL="0" marR="0" rtl="0">
           <a:lnSpc>
             <a:spcPct val="100000"/>
           </a:lnSpc>
@@ -2286,7 +2286,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
+          <a:defRPr b="0" baseline="0" cap="none" i="0" kumimoji="0" normalizeH="0" spc="0" strike="noStrike" sz="1800" u="none">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -2316,33 +2316,33 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
-  <sheetFormatPr defaultColWidth="10" defaultRowHeight="13" customHeight="1" outlineLevelCol="4"/>
+  <dimension ref="A1:F12"/>
+  <sheetFormatPr customHeight="1" defaultColWidth="10" defaultRowHeight="13" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="2" style="1" customWidth="1" collapsed="1"/>
-    <col min="2" max="4" width="30.5092592592593" style="1" customWidth="1" collapsed="1"/>
-    <col min="5" max="256" width="10" style="1" customWidth="1" collapsed="1"/>
+    <col min="1" max="1" customWidth="true" style="1" width="2.0" collapsed="true"/>
+    <col min="2" max="4" customWidth="true" style="1" width="30.5092592592593" collapsed="true"/>
+    <col min="5" max="256" customWidth="true" style="1" width="10.0" collapsed="true"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1" spans="1:5">
+    <row customHeight="1" ht="15" r="1" spans="1:5">
       <c r="A1" s="15"/>
       <c r="B1" s="16"/>
       <c r="C1" s="16"/>
       <c r="D1" s="16"/>
       <c r="E1" s="17"/>
     </row>
-    <row r="2" ht="15" customHeight="1" spans="1:5">
+    <row customHeight="1" ht="15" r="2" spans="1:5">
       <c r="A2" s="18"/>
       <c r="B2" s="19"/>
       <c r="C2" s="19"/>
       <c r="D2" s="19"/>
       <c r="E2" s="20"/>
     </row>
-    <row r="3" ht="8" customHeight="1" spans="1:5">
+    <row customHeight="1" ht="8" r="3" spans="1:5">
       <c r="A3" s="18"/>
       <c r="B3" s="21" t="s">
         <v>0</v>
@@ -2351,28 +2351,28 @@
       <c r="D3" s="19"/>
       <c r="E3" s="20"/>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:5">
+    <row customHeight="1" ht="15" r="4" spans="1:5">
       <c r="A4" s="18"/>
       <c r="B4" s="19"/>
       <c r="C4" s="19"/>
       <c r="D4" s="19"/>
       <c r="E4" s="20"/>
     </row>
-    <row r="5" ht="15" customHeight="1" spans="1:5">
+    <row customHeight="1" ht="15" r="5" spans="1:5">
       <c r="A5" s="18"/>
       <c r="B5" s="19"/>
       <c r="C5" s="19"/>
       <c r="D5" s="19"/>
       <c r="E5" s="20"/>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:5">
+    <row customHeight="1" ht="15" r="6" spans="1:5">
       <c r="A6" s="18"/>
       <c r="B6" s="19"/>
       <c r="C6" s="19"/>
       <c r="D6" s="19"/>
       <c r="E6" s="20"/>
     </row>
-    <row r="7" ht="19" customHeight="1" spans="1:5">
+    <row customHeight="1" ht="19" r="7" spans="1:5">
       <c r="A7" s="18"/>
       <c r="B7" s="22" t="s">
         <v>1</v>
@@ -2385,14 +2385,14 @@
       </c>
       <c r="E7" s="20"/>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:5">
+    <row customHeight="1" ht="15" r="8" spans="1:5">
       <c r="A8" s="18"/>
       <c r="B8" s="19"/>
       <c r="C8" s="19"/>
       <c r="D8" s="19"/>
       <c r="E8" s="20"/>
     </row>
-    <row r="9" ht="17" customHeight="1" spans="1:5">
+    <row customHeight="1" ht="17" r="9" spans="1:5">
       <c r="A9" s="18"/>
       <c r="B9" s="23" t="s">
         <v>4</v>
@@ -2401,7 +2401,7 @@
       <c r="D9" s="24"/>
       <c r="E9" s="20"/>
     </row>
-    <row r="10" ht="17" customHeight="1" spans="1:5">
+    <row customHeight="1" ht="17" r="10" spans="1:5">
       <c r="A10" s="18"/>
       <c r="B10" s="25"/>
       <c r="C10" s="26" t="s">
@@ -2412,7 +2412,7 @@
       </c>
       <c r="E10" s="20"/>
     </row>
-    <row r="11" ht="17" customHeight="1" spans="1:5">
+    <row customHeight="1" ht="17" r="11" spans="1:5">
       <c r="A11" s="18"/>
       <c r="B11" s="23" t="s">
         <v>7</v>
@@ -2421,7 +2421,7 @@
       <c r="D11" s="24"/>
       <c r="E11" s="20"/>
     </row>
-    <row r="12" ht="17" customHeight="1" spans="1:5">
+    <row customHeight="1" ht="17" r="12" spans="1:5">
       <c r="A12" s="28"/>
       <c r="B12" s="29"/>
       <c r="C12" s="30" t="s">
@@ -2436,8 +2436,8 @@
   <mergeCells count="1">
     <mergeCell ref="B3:D3"/>
   </mergeCells>
-  <pageMargins left="1" right="1" top="1" bottom="1" header="0.25" footer="0.25"/>
-  <pageSetup paperSize="1" orientation="portrait" useFirstPageNumber="1"/>
+  <pageMargins bottom="1" footer="0.25" header="0.25" left="1" right="1" top="1"/>
+  <pageSetup orientation="portrait" paperSize="1" useFirstPageNumber="1"/>
   <headerFooter>
     <oddFooter>&amp;C&amp;"Helvetica Neue,Regular"&amp;12&amp;K000000&amp;P</oddFooter>
   </headerFooter>
@@ -2445,26 +2445,26 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <sheetPr/>
-  <dimension ref="A1:X10"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.45" customHeight="1"/>
+  <dimension ref="A1:Y10"/>
+  <sheetFormatPr customHeight="1" defaultColWidth="9" defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="1" width="9" style="1" customWidth="1"/>
-    <col min="2" max="2" width="14.3518518518519" style="1" customWidth="1"/>
-    <col min="3" max="4" width="17" style="1" customWidth="1"/>
-    <col min="5" max="5" width="9" style="1" customWidth="1"/>
-    <col min="6" max="6" width="88.8518518518518" style="1" customWidth="1"/>
-    <col min="7" max="7" width="34.1759259259259" style="1" customWidth="1"/>
-    <col min="8" max="9" width="9" style="1" customWidth="1"/>
-    <col min="10" max="10" width="13.5092592592593" style="1" customWidth="1"/>
-    <col min="11" max="11" width="42" style="1" customWidth="1"/>
-    <col min="12" max="12" width="27.5092592592593" style="1" customWidth="1"/>
-    <col min="13" max="18" width="73.3518518518518" style="1" customWidth="1"/>
-    <col min="19" max="257" width="9" style="1" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" style="1" width="9.0" collapsed="true"/>
+    <col min="2" max="2" customWidth="true" style="1" width="14.3518518518519" collapsed="true"/>
+    <col min="3" max="4" customWidth="true" style="1" width="17.0" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="1" width="9.0" collapsed="true"/>
+    <col min="6" max="6" customWidth="true" style="1" width="88.8518518518518" collapsed="true"/>
+    <col min="7" max="7" customWidth="true" style="1" width="34.1759259259259" collapsed="true"/>
+    <col min="8" max="9" customWidth="true" style="1" width="9.0" collapsed="true"/>
+    <col min="10" max="10" customWidth="true" style="1" width="13.5092592592593" collapsed="true"/>
+    <col min="11" max="11" customWidth="true" style="1" width="42.0" collapsed="true"/>
+    <col min="12" max="12" customWidth="true" style="1" width="27.5092592592593" collapsed="true"/>
+    <col min="13" max="18" customWidth="true" style="1" width="73.3518518518518" collapsed="true"/>
+    <col min="19" max="257" customWidth="true" style="1" width="9.0" collapsed="true"/>
   </cols>
   <sheetData>
-    <row r="1" ht="13.5" customHeight="1" spans="1:24">
+    <row customHeight="1" ht="13.5" r="1" spans="1:24">
       <c r="A1" s="3" t="s">
         <v>9</v>
       </c>
@@ -2538,7 +2538,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="2" ht="13.5" customHeight="1" spans="1:24">
+    <row customHeight="1" ht="13.5" r="2" spans="1:24">
       <c r="A2" s="9">
         <v>1</v>
       </c>
@@ -2592,7 +2592,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="3" ht="13.5" customHeight="1" spans="1:24">
+    <row customHeight="1" ht="13.5" r="3" spans="1:24">
       <c r="A3" s="9">
         <v>2</v>
       </c>
@@ -2654,7 +2654,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="4" ht="13.5" customHeight="1" spans="1:24">
+    <row customHeight="1" ht="13.5" r="4" spans="1:24">
       <c r="A4" s="4"/>
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
@@ -2678,7 +2678,7 @@
       <c r="Q4" s="14"/>
       <c r="R4" s="14"/>
     </row>
-    <row r="5" ht="13.5" customHeight="1" spans="1:24">
+    <row customHeight="1" ht="13.5" r="5" spans="1:24">
       <c r="A5" s="4"/>
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
@@ -2697,7 +2697,7 @@
       <c r="Q5" s="4"/>
       <c r="R5" s="4"/>
     </row>
-    <row r="6" ht="13.5" customHeight="1" spans="1:24">
+    <row customHeight="1" ht="13.5" r="6" spans="1:24">
       <c r="A6" s="4"/>
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
@@ -2717,7 +2717,7 @@
       <c r="Q6" s="4"/>
       <c r="R6" s="4"/>
     </row>
-    <row r="7" ht="13.5" customHeight="1" spans="1:24">
+    <row customHeight="1" ht="13.5" r="7" spans="1:24">
       <c r="A7" s="4"/>
       <c r="B7" s="4"/>
       <c r="C7" s="4"/>
@@ -2737,7 +2737,7 @@
       <c r="Q7" s="4"/>
       <c r="R7" s="4"/>
     </row>
-    <row r="8" ht="13.5" customHeight="1" spans="1:24">
+    <row customHeight="1" ht="13.5" r="8" spans="1:24">
       <c r="A8" s="4"/>
       <c r="B8" s="4"/>
       <c r="C8" s="4"/>
@@ -2757,7 +2757,7 @@
       <c r="Q8" s="4"/>
       <c r="R8" s="4"/>
     </row>
-    <row r="9" ht="13.5" customHeight="1" spans="1:24">
+    <row customHeight="1" ht="13.5" r="9" spans="1:24">
       <c r="A9" s="4"/>
       <c r="B9" s="4"/>
       <c r="C9" s="4"/>
@@ -2777,7 +2777,7 @@
       <c r="Q9" s="4"/>
       <c r="R9" s="4"/>
     </row>
-    <row r="10" ht="13.5" customHeight="1" spans="1:24">
+    <row customHeight="1" ht="13.5" r="10" spans="1:24">
       <c r="A10" s="4"/>
       <c r="B10" s="4"/>
       <c r="C10" s="4"/>
@@ -2799,10 +2799,10 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="T3" r:id="rId1" display="\\10.11.1.158\03. TEST Team\NLB SLO\FileShare\UAT" tooltip="\\10.11.1.158\03. TEST Team\NLB SLO\FileShare\UAT"/>
+    <hyperlink display="\\10.11.1.158\03. TEST Team\NLB SLO\FileShare\UAT" r:id="rId1" ref="T3" tooltip="\\10.11.1.158\03. TEST Team\NLB SLO\FileShare\UAT"/>
   </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" orientation="portrait" useFirstPageNumber="1"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageSetup orientation="portrait" paperSize="1" useFirstPageNumber="1"/>
   <headerFooter>
     <oddFooter>&amp;C&amp;"Helvetica Neue,Regular"&amp;12&amp;K000000&amp;P</oddFooter>
   </headerFooter>
@@ -2810,20 +2810,20 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <sheetPr/>
-  <dimension ref="A1:E10"/>
-  <sheetFormatPr defaultColWidth="8.82407407407407" defaultRowHeight="14.45" customHeight="1" outlineLevelCol="4"/>
+  <dimension ref="A1:F10"/>
+  <sheetFormatPr customHeight="1" defaultColWidth="8.82407407407407" defaultRowHeight="14.45" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="12.6759259259259" style="1" customWidth="1" collapsed="1"/>
-    <col min="2" max="2" width="68.3518518518518" style="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="7.50925925925926" style="1" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="11.6759259259259" style="1" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="9.67592592592593" style="1" customWidth="1" collapsed="1"/>
-    <col min="6" max="256" width="8.85185185185185" style="1" customWidth="1" collapsed="1"/>
+    <col min="1" max="1" customWidth="true" style="1" width="12.6759259259259" collapsed="true"/>
+    <col min="2" max="2" customWidth="true" style="1" width="68.3518518518518" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="1" width="7.50925925925926" collapsed="true"/>
+    <col min="4" max="4" customWidth="true" style="1" width="11.6759259259259" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="1" width="9.67592592592593" collapsed="true"/>
+    <col min="6" max="256" customWidth="true" style="1" width="8.85185185185185" collapsed="true"/>
   </cols>
   <sheetData>
-    <row r="1" ht="13.5" customHeight="1" spans="1:5">
+    <row customHeight="1" ht="13.5" r="1" spans="1:5">
       <c r="A1" s="2" t="s">
         <v>13</v>
       </c>
@@ -2840,7 +2840,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" ht="13.5" customHeight="1" spans="1:5">
+    <row customHeight="1" ht="13.5" r="2" spans="1:5">
       <c r="A2" s="3" t="s">
         <v>36</v>
       </c>
@@ -2851,7 +2851,7 @@
       <c r="D2" s="4"/>
       <c r="E2" s="4"/>
     </row>
-    <row r="3" ht="13.5" customHeight="1" spans="1:5">
+    <row customHeight="1" ht="13.5" r="3" spans="1:5">
       <c r="A3" s="3" t="s">
         <v>43</v>
       </c>
@@ -2868,7 +2868,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="4" ht="13.5" customHeight="1" spans="1:5">
+    <row customHeight="1" ht="13.5" r="4" spans="1:5">
       <c r="A4" s="3" t="s">
         <v>62</v>
       </c>
@@ -2879,7 +2879,7 @@
       <c r="D4" s="4"/>
       <c r="E4" s="4"/>
     </row>
-    <row r="5" ht="13.5" customHeight="1" spans="1:5">
+    <row customHeight="1" ht="13.5" r="5" spans="1:5">
       <c r="A5" s="3" t="s">
         <v>51</v>
       </c>
@@ -2890,35 +2890,35 @@
       <c r="D5" s="4"/>
       <c r="E5" s="4"/>
     </row>
-    <row r="6" ht="13.5" customHeight="1" spans="1:5">
+    <row customHeight="1" ht="13.5" r="6" spans="1:5">
       <c r="A6" s="4"/>
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
       <c r="D6" s="4"/>
       <c r="E6" s="4"/>
     </row>
-    <row r="7" ht="13.5" customHeight="1" spans="1:5">
+    <row customHeight="1" ht="13.5" r="7" spans="1:5">
       <c r="A7" s="4"/>
       <c r="B7" s="4"/>
       <c r="C7" s="4"/>
       <c r="D7" s="4"/>
       <c r="E7" s="4"/>
     </row>
-    <row r="8" ht="13.5" customHeight="1" spans="1:5">
+    <row customHeight="1" ht="13.5" r="8" spans="1:5">
       <c r="A8" s="4"/>
       <c r="B8" s="4"/>
       <c r="C8" s="4"/>
       <c r="D8" s="4"/>
       <c r="E8" s="4"/>
     </row>
-    <row r="9" ht="13.5" customHeight="1" spans="1:5">
+    <row customHeight="1" ht="13.5" r="9" spans="1:5">
       <c r="A9" s="4"/>
       <c r="B9" s="4"/>
       <c r="C9" s="4"/>
       <c r="D9" s="4"/>
       <c r="E9" s="4"/>
     </row>
-    <row r="10" ht="13.5" customHeight="1" spans="1:5">
+    <row customHeight="1" ht="13.5" r="10" spans="1:5">
       <c r="A10" s="4"/>
       <c r="B10" s="4"/>
       <c r="C10" s="4"/>
@@ -2926,8 +2926,8 @@
       <c r="E10" s="4"/>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="1" orientation="portrait" useFirstPageNumber="1"/>
+  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageSetup orientation="portrait" paperSize="1" useFirstPageNumber="1"/>
   <headerFooter>
     <oddFooter>&amp;C&amp;"Helvetica Neue,Regular"&amp;12&amp;K000000&amp;P</oddFooter>
   </headerFooter>
